--- a/analysis/petstore_legacy_user_flows_first_2.xlsx
+++ b/analysis/petstore_legacy_user_flows_first_2.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User Flows" sheetId="1" r:id="R9c7c07ea02884c62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User Flows" sheetId="1" r:id="Rfe4a0143758a4892"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -675,13 +675,13 @@
         <x:v>Happy path</x:v>
       </x:c>
       <x:c r="D7" s="61" t="str">
-        <x:v>Returning customer can open the sign-in screen from the header or after requesting a protected page.</x:v>
+        <x:v>Returning customer can start sign-in from the store experience or after requesting protected functionality.</x:v>
       </x:c>
       <x:c r="E7" s="61" t="str">
-        <x:v>The customer can open a sign-in form from the store header or when they try to access an area that requires authentication. The same entry point also guides new customers toward account creation.</x:v>
+        <x:v>The customer can start authentication from the normal store entry points or when they try to use functionality that requires identity. The same entry point also guides new customers toward account creation.</x:v>
       </x:c>
       <x:c r="F7" s="61" t="str">
-        <x:v>The user sees fields for login and password, a sign-in action, and an option to create a new account.</x:v>
+        <x:v>The user is asked for login and password and can choose to create a new account instead.</x:v>
       </x:c>
       <x:c r="G7" s="61" t="str">
         <x:v>Yes</x:v>
@@ -769,7 +769,7 @@
         <x:v>After a successful sign-in, the store recognizes the customer as signed in for subsequent account, checkout, and order actions.</x:v>
       </x:c>
       <x:c r="F9" s="61" t="str">
-        <x:v>Header changes from Sign in to Sign out; protected pages become accessible.</x:v>
+        <x:v>The system shows the customer as signed in and protected functionality becomes accessible.</x:v>
       </x:c>
       <x:c r="G9" s="61" t="str">
         <x:v>Yes</x:v>
@@ -807,13 +807,13 @@
         <x:v>Happy path</x:v>
       </x:c>
       <x:c r="D10" s="61" t="str">
-        <x:v>Successful login returns the customer to the page they originally tried to open.</x:v>
+        <x:v>Successful login returns the customer to the functionality they originally requested.</x:v>
       </x:c>
       <x:c r="E10" s="61" t="str">
-        <x:v>If the customer was asked to sign in before opening a protected page, the system remembers where they were going and continues there after successful sign-in.</x:v>
+        <x:v>If the customer was asked to sign in before using protected functionality, the system remembers the intended destination and continues there after successful sign-in.</x:v>
       </x:c>
       <x:c r="F10" s="61" t="str">
-        <x:v>Customer lands on the original protected page instead of a generic success page.</x:v>
+        <x:v>The customer continues to the originally requested capability instead of a generic success destination.</x:v>
       </x:c>
       <x:c r="G10" s="61" t="str">
         <x:v>Yes</x:v>
@@ -854,7 +854,7 @@
         <x:v>Remember user name stores only the login name for future convenience.</x:v>
       </x:c>
       <x:c r="E11" s="63" t="str">
-        <x:v>If the user chooses to be remembered, the system pre-fills the last used login name on the sign-in form next time. The password is still required.</x:v>
+        <x:v>If the user chooses to be remembered, the system pre-fills the last used login name the next time authentication is requested. The password is still required.</x:v>
       </x:c>
       <x:c r="F11" s="63" t="str">
         <x:v>Next visit pre-fills the user name; password field remains separate.</x:v>
@@ -895,7 +895,7 @@
         <x:v>Alternative path</x:v>
       </x:c>
       <x:c r="D12" s="61" t="str">
-        <x:v>Invalid user name or password sends the customer to a sign-in error page.</x:v>
+        <x:v>Invalid user name or password shows a sign-in error.</x:v>
       </x:c>
       <x:c r="E12" s="61" t="str">
         <x:v>If the login name or password is incorrect, the system rejects the sign-in attempt without signing in the customer.</x:v>
@@ -939,13 +939,13 @@
         <x:v>Alternative path</x:v>
       </x:c>
       <x:c r="D13" s="61" t="str">
-        <x:v>Protected pages require login before access.</x:v>
+        <x:v>Protected functionality requires login before access.</x:v>
       </x:c>
       <x:c r="E13" s="61" t="str">
-        <x:v>When a signed-out customer tries to open account, checkout, order, or other protected areas, the system asks for login and password before showing that page.</x:v>
+        <x:v>When a signed-out customer tries to use account, checkout, order, or other protected functionality, the system asks for login and password before continuing.</x:v>
       </x:c>
       <x:c r="F13" s="61" t="str">
-        <x:v>Customer cannot continue to protected content until login succeeds.</x:v>
+        <x:v>The customer cannot continue to protected functionality until login succeeds.</x:v>
       </x:c>
       <x:c r="G13" s="61" t="str">
         <x:v>Yes</x:v>
@@ -983,13 +983,13 @@
         <x:v>Gap / deferred</x:v>
       </x:c>
       <x:c r="D14" s="64" t="str">
-        <x:v>Direct sign-in from the header does not define a clear post-login destination in the inspected legacy code.</x:v>
+        <x:v>Direct sign-in does not define a clear post-login destination in the inspected legacy code.</x:v>
       </x:c>
       <x:c r="E14" s="64" t="str">
-        <x:v>When sign-in is opened directly from the header, the expected page after successful sign-in is not clearly defined in the legacy behavior.</x:v>
+        <x:v>When sign-in is started directly rather than as part of a protected action, the expected destination after successful sign-in is not clearly defined in the legacy behavior.</x:v>
       </x:c>
       <x:c r="F14" s="64" t="str">
-        <x:v>Needs confirmation in runtime or migration design: expected default landing page after direct login.</x:v>
+        <x:v>Needs confirmation in runtime or migration design: expected default destination after direct login.</x:v>
       </x:c>
       <x:c r="G14" s="64" t="str">
         <x:v>Partially</x:v>
@@ -1027,7 +1027,7 @@
         <x:v>Happy path</x:v>
       </x:c>
       <x:c r="D15" s="61" t="str">
-        <x:v>New customer can start account creation from the Sign In page.</x:v>
+        <x:v>New customer can start account creation from the sign-in experience.</x:v>
       </x:c>
       <x:c r="E15" s="61" t="str">
         <x:v>A new customer can start registration from the sign-in experience by choosing to create an account.</x:v>
@@ -1077,7 +1077,7 @@
         <x:v>After the user provides a new login name and password, the system creates the account identity used for the rest of registration.</x:v>
       </x:c>
       <x:c r="F16" s="61" t="str">
-        <x:v>Customer proceeds to the account-information form.</x:v>
+        <x:v>Customer proceeds to provide account information.</x:v>
       </x:c>
       <x:c r="G16" s="61" t="str">
         <x:v>Yes</x:v>
@@ -1165,7 +1165,7 @@
         <x:v>After the customer submits account details, the system saves the customer profile and treats the customer as signed in.</x:v>
       </x:c>
       <x:c r="F18" s="64" t="str">
-        <x:v>Header shows Sign out; customer can use account and checkout flows as an authenticated customer.</x:v>
+        <x:v>The system shows the customer as signed in; account and checkout flows are available as authenticated functionality.</x:v>
       </x:c>
       <x:c r="G18" s="64" t="str">
         <x:v>Yes</x:v>
@@ -1253,7 +1253,7 @@
         <x:v>The system expects required customer information before creating a complete customer account. Missing required information should stop or block the account-details step.</x:v>
       </x:c>
       <x:c r="F20" s="64" t="str">
-        <x:v>Runtime display behavior needs confirmation; code detects missing fields, but the inspected mapping does not show a dedicated friendly error screen for this exact case.</x:v>
+        <x:v>Runtime feedback behavior needs confirmation; code detects missing fields, but the inspected flow does not show a dedicated friendly error for this exact case.</x:v>
       </x:c>
       <x:c r="G20" s="64" t="str">
         <x:v>Partially</x:v>
@@ -1294,7 +1294,7 @@
         <x:v>Repeated password field is shown but not enforced in the inspected account-creation action.</x:v>
       </x:c>
       <x:c r="E21" s="64" t="str">
-        <x:v>The legacy registration screen asks the customer to repeat the password, but the inspected behavior does not confirm that the two password values match before account creation.</x:v>
+        <x:v>The legacy registration experience asks the customer to repeat the password, but the inspected behavior does not confirm that the two password values match before account creation.</x:v>
       </x:c>
       <x:c r="F21" s="64" t="str">
         <x:v>Business rule should be decided for migration: either enforce matching passwords or remove the field.</x:v>
@@ -1335,10 +1335,10 @@
         <x:v>Gap / deferred</x:v>
       </x:c>
       <x:c r="D22" s="57" t="str">
-        <x:v>Account information form contains demo default values.</x:v>
+        <x:v>Account information step contains demo default values.</x:v>
       </x:c>
       <x:c r="E22" s="57" t="str">
-        <x:v>The legacy account form shows sample customer data by default. For a real customer-facing system, the expected behavior should be explicitly decided.</x:v>
+        <x:v>The legacy account-information step shows sample customer data by default. For a real customer-facing system, the expected behavior should be explicitly decided.</x:v>
       </x:c>
       <x:c r="F22" s="57" t="str">
         <x:v>Migration should decide whether defaults are only demo data or should be removed for real users.</x:v>

--- a/analysis/petstore_legacy_user_flows_first_2.xlsx
+++ b/analysis/petstore_legacy_user_flows_first_2.xlsx
@@ -1,19 +1,11 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User Flows" sheetId="1" r:id="Rfe4a0143758a4892"/>
-  </x:sheets>
-</x:workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="8">
+  <x:fonts count="9">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -48,6 +40,12 @@
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF7F0000"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
       <x:sz val="11"/>
       <x:color rgb="FF7F0000"/>
       <x:name val="Carlito"/>
@@ -59,7 +57,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="15">
+  <x:fills count="16">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -124,6 +122,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF8064A2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEA9999"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -152,7 +155,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="67">
+  <x:cellXfs count="69">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -285,10 +288,13 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -300,16 +306,19 @@
     <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="8" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -319,7 +328,7 @@
 </x:styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
   <a:themeElements>
     <a:clrScheme name="ChatGPT">
@@ -510,8 +519,19 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheets>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User Flows" sheetId="1" r:id="R82b9c19f72924e70"/>
+  </x:sheets>
+</x:workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="0"/>
+  </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="10.630000114440918" hidden="0" customWidth="1"/>
@@ -664,707 +684,691 @@
         <x:v>SDD evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="66" customHeight="1">
-      <x:c r="A7" s="59" t="str">
+    <x:row r="7" ht="37.5" customHeight="1" collapsed="1">
+      <x:c r="A7" s="60" t="str">
         <x:v>UF-001</x:v>
       </x:c>
-      <x:c r="B7" s="59" t="str">
+      <x:c r="B7" s="60" t="str">
         <x:v>User login</x:v>
       </x:c>
       <x:c r="C7" s="60" t="str">
+        <x:v>Not Passed - Missed</x:v>
+      </x:c>
+      <x:c r="D7" s="60" t="str">
+        <x:v>At least one source behavior is missing in destination and not covered/deferred in SDD.</x:v>
+      </x:c>
+      <x:c r="E7" s="60" t="str"/>
+      <x:c r="F7" s="60" t="str"/>
+      <x:c r="G7" s="60" t="str"/>
+      <x:c r="H7" s="60" t="str"/>
+      <x:c r="I7" s="60" t="str"/>
+      <x:c r="J7" s="60" t="str"/>
+      <x:c r="K7" s="60" t="str"/>
+      <x:c r="L7" s="60" t="str"/>
+      <x:c r="M7" s="60" t="str"/>
+      <x:c r="N7" s="60" t="str"/>
+    </x:row>
+    <x:row r="8" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A8" s="61" t="str"/>
+      <x:c r="B8" s="61" t="str"/>
+      <x:c r="C8" s="61" t="str">
         <x:v>Happy path</x:v>
       </x:c>
-      <x:c r="D7" s="61" t="str">
+      <x:c r="D8" s="62" t="str">
         <x:v>Returning customer can start sign-in from the store experience or after requesting protected functionality.</x:v>
       </x:c>
-      <x:c r="E7" s="61" t="str">
+      <x:c r="E8" s="62" t="str">
         <x:v>The customer can start authentication from the normal store entry points or when they try to use functionality that requires identity. The same entry point also guides new customers toward account creation.</x:v>
       </x:c>
-      <x:c r="F7" s="61" t="str">
+      <x:c r="F8" s="62" t="str">
         <x:v>The user is asked for login and password and can choose to create a new account instead.</x:v>
       </x:c>
-      <x:c r="G7" s="61" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="H7" s="61" t="str">
+      <x:c r="G8" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H8" s="62" t="str">
         <x:v>signon.jsp; banner.jsp; signon-config.xml</x:v>
       </x:c>
-      <x:c r="I7" s="61" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="J7" s="61" t="str">
+      <x:c r="I8" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J8" s="62" t="str">
         <x:v>Angular shell has a Sign in link; protected customer routes redirect anonymous users to /signin with returnUrl.</x:v>
       </x:c>
-      <x:c r="K7" s="61" t="str">
+      <x:c r="K8" s="62" t="str">
         <x:v>catalog-shell.component.ts; auth.guard.ts; app.routes.ts</x:v>
       </x:c>
-      <x:c r="L7" s="61" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="M7" s="61" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="N7" s="61" t="str">
+      <x:c r="L8" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M8" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N8" s="62" t="str">
         <x:v>specs/005-account-ui/spec.md FR-001, FR-006; specs/005-account-ui/plan.md DD-003</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="66" customHeight="1">
-      <x:c r="A8" s="59" t="str">
-        <x:v>UF-001</x:v>
-      </x:c>
-      <x:c r="B8" s="59" t="str">
-        <x:v>User login</x:v>
-      </x:c>
-      <x:c r="C8" s="60" t="str">
+    <x:row r="9" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A9" s="61" t="str"/>
+      <x:c r="B9" s="61" t="str"/>
+      <x:c r="C9" s="61" t="str">
         <x:v>Happy path</x:v>
       </x:c>
-      <x:c r="D8" s="61" t="str">
+      <x:c r="D9" s="62" t="str">
         <x:v>System validates the submitted user name and password against registered users.</x:v>
       </x:c>
-      <x:c r="E8" s="61" t="str">
+      <x:c r="E9" s="62" t="str">
         <x:v>When the customer submits login details, the system checks that the account exists and that the password is correct.</x:v>
       </x:c>
-      <x:c r="F8" s="61" t="str">
+      <x:c r="F9" s="62" t="str">
         <x:v>Valid credentials are accepted; invalid credentials are rejected.</x:v>
       </x:c>
-      <x:c r="G8" s="61" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="H8" s="61" t="str">
+      <x:c r="G9" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H9" s="62" t="str">
         <x:v>SignOnFilter.java; SignOnEJB.java</x:v>
       </x:c>
-      <x:c r="I8" s="61" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="J8" s="61" t="str">
+      <x:c r="I9" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J9" s="62" t="str">
         <x:v>Backend verifies user id/password and issues a JWT only when the password hash matches.</x:v>
       </x:c>
-      <x:c r="K8" s="61" t="str">
+      <x:c r="K9" s="62" t="str">
         <x:v>AuthController.cs; Pbkdf2PasswordHasher.cs</x:v>
       </x:c>
-      <x:c r="L8" s="61" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="M8" s="61" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="N8" s="61" t="str">
+      <x:c r="L9" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M9" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N9" s="62" t="str">
         <x:v>specs/004-customer-accounts/spec.md FR-003, FR-008; specs/004-customer-accounts/plan.md DD-001</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="66" customHeight="1">
-      <x:c r="A9" s="59" t="str">
-        <x:v>UF-001</x:v>
-      </x:c>
-      <x:c r="B9" s="59" t="str">
-        <x:v>User login</x:v>
-      </x:c>
-      <x:c r="C9" s="60" t="str">
+    <x:row r="10" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A10" s="61" t="str"/>
+      <x:c r="B10" s="61" t="str"/>
+      <x:c r="C10" s="61" t="str">
         <x:v>Happy path</x:v>
       </x:c>
-      <x:c r="D9" s="61" t="str">
+      <x:c r="D10" s="62" t="str">
         <x:v>Successful login creates a signed-in session for the user.</x:v>
       </x:c>
-      <x:c r="E9" s="61" t="str">
+      <x:c r="E10" s="62" t="str">
         <x:v>After a successful sign-in, the store recognizes the customer as signed in for subsequent account, checkout, and order actions.</x:v>
       </x:c>
-      <x:c r="F9" s="61" t="str">
+      <x:c r="F10" s="62" t="str">
         <x:v>The system shows the customer as signed in and protected functionality becomes accessible.</x:v>
       </x:c>
-      <x:c r="G9" s="61" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="H9" s="61" t="str">
+      <x:c r="G10" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H10" s="62" t="str">
         <x:v>SignOnFilter.java; banner.jsp</x:v>
       </x:c>
-      <x:c r="I9" s="61" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="J9" s="61" t="str">
+      <x:c r="I10" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J10" s="62" t="str">
         <x:v>Destination uses JWT identity in Angular instead of a legacy server session; header shows user id and Sign out while signed in.</x:v>
       </x:c>
-      <x:c r="K9" s="61" t="str">
+      <x:c r="K10" s="62" t="str">
         <x:v>identity.service.ts; catalog-shell.component.ts; auth.interceptor.ts</x:v>
       </x:c>
-      <x:c r="L9" s="61" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="M9" s="61" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="N9" s="61" t="str">
+      <x:c r="L10" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M10" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N10" s="62" t="str">
         <x:v>specs/004-customer-accounts/plan.md DD-001; specs/005-account-ui/plan.md DD-001, DD-005</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="66" customHeight="1">
-      <x:c r="A10" s="59" t="str">
-        <x:v>UF-001</x:v>
-      </x:c>
-      <x:c r="B10" s="59" t="str">
-        <x:v>User login</x:v>
-      </x:c>
-      <x:c r="C10" s="60" t="str">
+    <x:row r="11" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A11" s="61" t="str"/>
+      <x:c r="B11" s="61" t="str"/>
+      <x:c r="C11" s="61" t="str">
         <x:v>Happy path</x:v>
       </x:c>
-      <x:c r="D10" s="61" t="str">
+      <x:c r="D11" s="62" t="str">
         <x:v>Successful login returns the customer to the functionality they originally requested.</x:v>
       </x:c>
-      <x:c r="E10" s="61" t="str">
+      <x:c r="E11" s="62" t="str">
         <x:v>If the customer was asked to sign in before using protected functionality, the system remembers the intended destination and continues there after successful sign-in.</x:v>
       </x:c>
-      <x:c r="F10" s="61" t="str">
+      <x:c r="F11" s="62" t="str">
         <x:v>The customer continues to the originally requested capability instead of a generic success destination.</x:v>
       </x:c>
-      <x:c r="G10" s="61" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="H10" s="61" t="str">
+      <x:c r="G11" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H11" s="62" t="str">
         <x:v>SignOnFilter.java; signon-config.xml</x:v>
       </x:c>
-      <x:c r="I10" s="61" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="J10" s="61" t="str">
+      <x:c r="I11" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J11" s="62" t="str">
         <x:v>authGuard stores the requested route as returnUrl; SignInComponent navigates back to it after successful sign-in.</x:v>
       </x:c>
-      <x:c r="K10" s="61" t="str">
+      <x:c r="K11" s="62" t="str">
         <x:v>auth.guard.ts; sign-in.component.ts</x:v>
       </x:c>
-      <x:c r="L10" s="61" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="M10" s="61" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="N10" s="61" t="str">
+      <x:c r="L11" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M11" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N11" s="62" t="str">
         <x:v>specs/005-account-ui/plan.md DD-003</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="66" customHeight="1">
-      <x:c r="A11" s="59" t="str">
-        <x:v>UF-001</x:v>
-      </x:c>
-      <x:c r="B11" s="59" t="str">
-        <x:v>User login</x:v>
-      </x:c>
-      <x:c r="C11" s="60" t="str">
+    <x:row r="12" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A12" s="61" t="str"/>
+      <x:c r="B12" s="61" t="str"/>
+      <x:c r="C12" s="61" t="str">
         <x:v>Happy path</x:v>
       </x:c>
-      <x:c r="D11" s="63" t="str">
+      <x:c r="D12" s="64" t="str">
         <x:v>Remember user name stores only the login name for future convenience.</x:v>
       </x:c>
-      <x:c r="E11" s="63" t="str">
+      <x:c r="E12" s="64" t="str">
         <x:v>If the user chooses to be remembered, the system pre-fills the last used login name the next time authentication is requested. The password is still required.</x:v>
       </x:c>
-      <x:c r="F11" s="63" t="str">
+      <x:c r="F12" s="64" t="str">
         <x:v>Next visit pre-fills the user name; password field remains separate.</x:v>
       </x:c>
-      <x:c r="G11" s="63" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="H11" s="63" t="str">
+      <x:c r="G12" s="64" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H12" s="64" t="str">
         <x:v>signon.jsp; SignOnFilter.java</x:v>
       </x:c>
-      <x:c r="I11" s="63" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="J11" s="63" t="str">
+      <x:c r="I12" s="64" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="J12" s="64" t="str">
         <x:v>No remember-user-name checkbox/cookie exists in the Angular sign-in flow. The destination stores JWT identity for session restore, not a username convenience cookie.</x:v>
       </x:c>
-      <x:c r="K11" s="63" t="str">
+      <x:c r="K12" s="64" t="str">
         <x:v>sign-in.component.ts; identity.service.ts</x:v>
       </x:c>
-      <x:c r="L11" s="63" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="M11" s="63" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="N11" s="63" t="str">
+      <x:c r="L12" s="64" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="M12" s="64" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N12" s="64" t="str">
         <x:v>No matching SDD requirement or deferral found in specs/004-customer-accounts or specs/005-account-ui.</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="66" customHeight="1">
-      <x:c r="A12" s="59" t="str">
-        <x:v>UF-001</x:v>
-      </x:c>
-      <x:c r="B12" s="59" t="str">
-        <x:v>User login</x:v>
-      </x:c>
-      <x:c r="C12" s="60" t="str">
+    <x:row r="13" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A13" s="61" t="str"/>
+      <x:c r="B13" s="61" t="str"/>
+      <x:c r="C13" s="61" t="str">
         <x:v>Alternative path</x:v>
       </x:c>
-      <x:c r="D12" s="61" t="str">
+      <x:c r="D13" s="62" t="str">
         <x:v>Invalid user name or password shows a sign-in error.</x:v>
       </x:c>
-      <x:c r="E12" s="61" t="str">
+      <x:c r="E13" s="62" t="str">
         <x:v>If the login name or password is incorrect, the system rejects the sign-in attempt without signing in the customer.</x:v>
       </x:c>
-      <x:c r="F12" s="61" t="str">
+      <x:c r="F13" s="62" t="str">
         <x:v>Customer sees a Sign-in Error message and is told to try again.</x:v>
       </x:c>
-      <x:c r="G12" s="61" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="H12" s="61" t="str">
+      <x:c r="G13" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H13" s="62" t="str">
         <x:v>SignOnFilter.java; signon_failed.jsp</x:v>
       </x:c>
-      <x:c r="I12" s="61" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="J12" s="61" t="str">
+      <x:c r="I13" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J13" s="62" t="str">
         <x:v>Backend returns the same invalid-credentials response for wrong password/unknown user; UI shows a generic error and clears the password.</x:v>
       </x:c>
-      <x:c r="K12" s="61" t="str">
+      <x:c r="K13" s="62" t="str">
         <x:v>AuthController.cs; sign-in.component.ts</x:v>
       </x:c>
-      <x:c r="L12" s="61" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="M12" s="61" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="N12" s="61" t="str">
+      <x:c r="L13" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M13" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N13" s="62" t="str">
         <x:v>specs/004-customer-accounts/spec.md FR-008; specs/005-account-ui/spec.md US1 scenario 2</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="66" customHeight="1">
-      <x:c r="A13" s="59" t="str">
-        <x:v>UF-001</x:v>
-      </x:c>
-      <x:c r="B13" s="59" t="str">
-        <x:v>User login</x:v>
-      </x:c>
-      <x:c r="C13" s="60" t="str">
+    <x:row r="14" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A14" s="61" t="str"/>
+      <x:c r="B14" s="61" t="str"/>
+      <x:c r="C14" s="61" t="str">
         <x:v>Alternative path</x:v>
       </x:c>
-      <x:c r="D13" s="61" t="str">
+      <x:c r="D14" s="62" t="str">
         <x:v>Protected functionality requires login before access.</x:v>
       </x:c>
-      <x:c r="E13" s="61" t="str">
+      <x:c r="E14" s="62" t="str">
         <x:v>When a signed-out customer tries to use account, checkout, order, or other protected functionality, the system asks for login and password before continuing.</x:v>
       </x:c>
-      <x:c r="F13" s="61" t="str">
+      <x:c r="F14" s="62" t="str">
         <x:v>The customer cannot continue to protected functionality until login succeeds.</x:v>
       </x:c>
-      <x:c r="G13" s="61" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="H13" s="61" t="str">
+      <x:c r="G14" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H14" s="62" t="str">
         <x:v>signon-config.xml; SignOnFilter.java</x:v>
       </x:c>
-      <x:c r="I13" s="61" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="J13" s="61" t="str">
+      <x:c r="I14" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J14" s="62" t="str">
         <x:v>Angular guards protect account, checkout, and order routes; backend authenticated account/order APIs also require authorization.</x:v>
       </x:c>
-      <x:c r="K13" s="61" t="str">
+      <x:c r="K14" s="62" t="str">
         <x:v>auth.guard.ts; app.routes.ts; AccountController.cs; OrdersController.cs</x:v>
       </x:c>
-      <x:c r="L13" s="61" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="M13" s="61" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="N13" s="61" t="str">
+      <x:c r="L14" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M14" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N14" s="62" t="str">
         <x:v>specs/005-account-ui/spec.md FR-006; specs/008-checkout-orders/spec.md checkout requires signed-in customer</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="66" customHeight="1">
-      <x:c r="A14" s="59" t="str">
-        <x:v>UF-001</x:v>
-      </x:c>
-      <x:c r="B14" s="59" t="str">
-        <x:v>User login</x:v>
-      </x:c>
-      <x:c r="C14" s="60" t="str">
+    <x:row r="15" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A15" s="61" t="str"/>
+      <x:c r="B15" s="61" t="str"/>
+      <x:c r="C15" s="61" t="str">
         <x:v>Gap / deferred</x:v>
       </x:c>
-      <x:c r="D14" s="64" t="str">
+      <x:c r="D15" s="65" t="str">
         <x:v>Direct sign-in does not define a clear post-login destination in the inspected legacy code.</x:v>
       </x:c>
-      <x:c r="E14" s="64" t="str">
+      <x:c r="E15" s="65" t="str">
         <x:v>When sign-in is started directly rather than as part of a protected action, the expected destination after successful sign-in is not clearly defined in the legacy behavior.</x:v>
       </x:c>
-      <x:c r="F14" s="64" t="str">
+      <x:c r="F15" s="65" t="str">
         <x:v>Needs confirmation in runtime or migration design: expected default destination after direct login.</x:v>
       </x:c>
-      <x:c r="G14" s="64" t="str">
+      <x:c r="G15" s="65" t="str">
         <x:v>Partially</x:v>
       </x:c>
-      <x:c r="H14" s="64" t="str">
+      <x:c r="H15" s="65" t="str">
         <x:v>banner.jsp; SignOnFilter.java</x:v>
       </x:c>
-      <x:c r="I14" s="64" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="J14" s="64" t="str">
+      <x:c r="I15" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J15" s="65" t="str">
         <x:v>Direct /signin without returnUrl lands on /catalog after success, so destination has a defined default.</x:v>
       </x:c>
-      <x:c r="K14" s="64" t="str">
+      <x:c r="K15" s="65" t="str">
         <x:v>sign-in.component.ts</x:v>
       </x:c>
-      <x:c r="L14" s="64" t="str">
+      <x:c r="L15" s="65" t="str">
         <x:v>Partially</x:v>
       </x:c>
-      <x:c r="M14" s="64" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="N14" s="64" t="str">
+      <x:c r="M15" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N15" s="65" t="str">
         <x:v>specs/005-account-ui/plan.md DD-003 covers returnUrl; default /catalog landing is not called out explicitly.</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="66" customHeight="1">
-      <x:c r="A15" s="59" t="str">
+    <x:row r="16" ht="37.5" customHeight="1" collapsed="1">
+      <x:c r="A16" s="67" t="str">
         <x:v>UF-002</x:v>
       </x:c>
-      <x:c r="B15" s="59" t="str">
+      <x:c r="B16" s="67" t="str">
         <x:v>New user account creation</x:v>
       </x:c>
-      <x:c r="C15" s="60" t="str">
+      <x:c r="C16" s="67" t="str">
+        <x:v>Not Passed - Deferred/Partial</x:v>
+      </x:c>
+      <x:c r="D16" s="67" t="str">
+        <x:v>At least one requirement is partial, deferred, or a known gap.</x:v>
+      </x:c>
+      <x:c r="E16" s="67" t="str"/>
+      <x:c r="F16" s="67" t="str"/>
+      <x:c r="G16" s="67" t="str"/>
+      <x:c r="H16" s="67" t="str"/>
+      <x:c r="I16" s="67" t="str"/>
+      <x:c r="J16" s="67" t="str"/>
+      <x:c r="K16" s="67" t="str"/>
+      <x:c r="L16" s="67" t="str"/>
+      <x:c r="M16" s="67" t="str"/>
+      <x:c r="N16" s="67" t="str"/>
+    </x:row>
+    <x:row r="17" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A17" s="61" t="str"/>
+      <x:c r="B17" s="61" t="str"/>
+      <x:c r="C17" s="61" t="str">
         <x:v>Happy path</x:v>
       </x:c>
-      <x:c r="D15" s="61" t="str">
+      <x:c r="D17" s="62" t="str">
         <x:v>New customer can start account creation from the sign-in experience.</x:v>
       </x:c>
-      <x:c r="E15" s="61" t="str">
+      <x:c r="E17" s="62" t="str">
         <x:v>A new customer can start registration from the sign-in experience by choosing to create an account.</x:v>
       </x:c>
-      <x:c r="F15" s="61" t="str">
+      <x:c r="F17" s="62" t="str">
         <x:v>Customer can submit Create New Account.</x:v>
       </x:c>
-      <x:c r="G15" s="61" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="H15" s="61" t="str">
+      <x:c r="G17" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H17" s="62" t="str">
         <x:v>signon.jsp; CreateUserHTMLAction.java</x:v>
       </x:c>
-      <x:c r="I15" s="61" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="J15" s="61" t="str">
+      <x:c r="I17" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J17" s="62" t="str">
         <x:v>The sign-in view links to a separate /register route instead of embedding registration on the same page.</x:v>
       </x:c>
-      <x:c r="K15" s="61" t="str">
+      <x:c r="K17" s="62" t="str">
         <x:v>sign-in.component.ts; register.component.ts; app.routes.ts</x:v>
       </x:c>
-      <x:c r="L15" s="61" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="M15" s="61" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="N15" s="61" t="str">
+      <x:c r="L17" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M17" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N17" s="62" t="str">
         <x:v>specs/005-account-ui/spec.md US2; specs/005-account-ui/plan.md DD-003</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="66" customHeight="1">
-      <x:c r="A16" s="59" t="str">
-        <x:v>UF-002</x:v>
-      </x:c>
-      <x:c r="B16" s="59" t="str">
-        <x:v>New user account creation</x:v>
-      </x:c>
-      <x:c r="C16" s="60" t="str">
+    <x:row r="18" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A18" s="61" t="str"/>
+      <x:c r="B18" s="61" t="str"/>
+      <x:c r="C18" s="61" t="str">
         <x:v>Happy path</x:v>
       </x:c>
-      <x:c r="D16" s="61" t="str">
+      <x:c r="D18" s="62" t="str">
         <x:v>Application creates a login record for a new user name and password.</x:v>
       </x:c>
-      <x:c r="E16" s="61" t="str">
+      <x:c r="E18" s="62" t="str">
         <x:v>After the user provides a new login name and password, the system creates the account identity used for the rest of registration.</x:v>
       </x:c>
-      <x:c r="F16" s="61" t="str">
+      <x:c r="F18" s="62" t="str">
         <x:v>Customer proceeds to provide account information.</x:v>
       </x:c>
-      <x:c r="G16" s="61" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="H16" s="61" t="str">
+      <x:c r="G18" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H18" s="62" t="str">
         <x:v>CreateUserHTMLAction.java; CreateUserEJBAction.java; SignOnEJB.java</x:v>
       </x:c>
-      <x:c r="I16" s="61" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="J16" s="61" t="str">
+      <x:c r="I18" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J18" s="62" t="str">
         <x:v>RegisterComponent posts user id/password/contact to POST /api/account; backend creates the user with hashed password.</x:v>
       </x:c>
-      <x:c r="K16" s="61" t="str">
+      <x:c r="K18" s="62" t="str">
         <x:v>register.component.ts; AccountController.cs; AccountRepository.cs</x:v>
       </x:c>
-      <x:c r="L16" s="61" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="M16" s="61" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="N16" s="61" t="str">
+      <x:c r="L18" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M18" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N18" s="62" t="str">
         <x:v>specs/004-customer-accounts/spec.md FR-001, FR-007; specs/005-account-ui/spec.md FR-004</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="66" customHeight="1">
-      <x:c r="A17" s="59" t="str">
-        <x:v>UF-002</x:v>
-      </x:c>
-      <x:c r="B17" s="59" t="str">
-        <x:v>New user account creation</x:v>
-      </x:c>
-      <x:c r="C17" s="60" t="str">
+    <x:row r="19" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A19" s="61" t="str"/>
+      <x:c r="B19" s="61" t="str"/>
+      <x:c r="C19" s="61" t="str">
         <x:v>Happy path</x:v>
       </x:c>
-      <x:c r="D17" s="64" t="str">
+      <x:c r="D19" s="65" t="str">
         <x:v>Customer enters account profile, contact, credit card, language, and preference information.</x:v>
       </x:c>
-      <x:c r="E17" s="64" t="str">
+      <x:c r="E19" s="65" t="str">
         <x:v>The customer provides the account details needed by the legacy store, including contact details, payment information, language, favorite category, and personalization preferences.</x:v>
       </x:c>
-      <x:c r="F17" s="64" t="str">
+      <x:c r="F19" s="65" t="str">
         <x:v>Customer can submit the complete account profile.</x:v>
       </x:c>
-      <x:c r="G17" s="64" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="H17" s="64" t="str">
+      <x:c r="G19" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H19" s="65" t="str">
         <x:v>create_customer.jsp; CustomerHTMLAction.java</x:v>
       </x:c>
-      <x:c r="I17" s="64" t="str">
+      <x:c r="I19" s="65" t="str">
         <x:v>Partially</x:v>
       </x:c>
-      <x:c r="J17" s="64" t="str">
+      <x:c r="J19" s="65" t="str">
         <x:v>Destination registration collects contact info, but not credit card, language, favorite category, MyList, or banner preferences.</x:v>
       </x:c>
-      <x:c r="K17" s="64" t="str">
+      <x:c r="K19" s="65" t="str">
         <x:v>register.component.ts; RegisterRequestDto.cs; AccountController.cs</x:v>
       </x:c>
-      <x:c r="L17" s="64" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="M17" s="66" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="N17" s="64" t="str">
+      <x:c r="L19" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M19" s="67" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="N19" s="65" t="str">
         <x:v>specs/004-customer-accounts/plan.md DD-003 no credit card storage, DD-004 profile preferences deferred; specs/005-account-ui/spec.md assumptions</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="66" customHeight="1">
-      <x:c r="A18" s="59" t="str">
-        <x:v>UF-002</x:v>
-      </x:c>
-      <x:c r="B18" s="59" t="str">
-        <x:v>New user account creation</x:v>
-      </x:c>
-      <x:c r="C18" s="60" t="str">
+    <x:row r="20" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A20" s="61" t="str"/>
+      <x:c r="B20" s="61" t="str"/>
+      <x:c r="C20" s="61" t="str">
         <x:v>Happy path</x:v>
       </x:c>
-      <x:c r="D18" s="64" t="str">
+      <x:c r="D20" s="65" t="str">
         <x:v>After profile submission, the system creates/updates customer data and signs the customer in.</x:v>
       </x:c>
-      <x:c r="E18" s="64" t="str">
+      <x:c r="E20" s="65" t="str">
         <x:v>After the customer submits account details, the system saves the customer profile and treats the customer as signed in.</x:v>
       </x:c>
-      <x:c r="F18" s="64" t="str">
+      <x:c r="F20" s="65" t="str">
         <x:v>The system shows the customer as signed in; account and checkout flows are available as authenticated functionality.</x:v>
       </x:c>
-      <x:c r="G18" s="64" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="H18" s="64" t="str">
+      <x:c r="G20" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H20" s="65" t="str">
         <x:v>CustomerHTMLAction.java; CustomerEJBAction.java; CreateUserFlowHandler.java</x:v>
       </x:c>
-      <x:c r="I18" s="64" t="str">
+      <x:c r="I20" s="65" t="str">
         <x:v>Partially</x:v>
       </x:c>
-      <x:c r="J18" s="64" t="str">
+      <x:c r="J20" s="65" t="str">
         <x:v>Destination creates account/contact and auto signs in, but payment/profile/preferences/locale are not part of account creation.</x:v>
       </x:c>
-      <x:c r="K18" s="64" t="str">
+      <x:c r="K20" s="65" t="str">
         <x:v>AccountController.cs; register.component.ts; identity.service.ts</x:v>
       </x:c>
-      <x:c r="L18" s="64" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="M18" s="66" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="N18" s="64" t="str">
+      <x:c r="L20" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M20" s="67" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="N20" s="65" t="str">
         <x:v>specs/005-account-ui/plan.md DD-004 auto sign-in; specs/004-customer-accounts/plan.md DD-003, DD-004 defer payment/profile data</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="66" customHeight="1">
-      <x:c r="A19" s="59" t="str">
-        <x:v>UF-002</x:v>
-      </x:c>
-      <x:c r="B19" s="59" t="str">
-        <x:v>New user account creation</x:v>
-      </x:c>
-      <x:c r="C19" s="60" t="str">
+    <x:row r="21" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A21" s="61" t="str"/>
+      <x:c r="B21" s="61" t="str"/>
+      <x:c r="C21" s="61" t="str">
         <x:v>Alternative path</x:v>
       </x:c>
-      <x:c r="D19" s="61" t="str">
+      <x:c r="D21" s="62" t="str">
         <x:v>Duplicate user name is rejected.</x:v>
       </x:c>
-      <x:c r="E19" s="61" t="str">
+      <x:c r="E21" s="62" t="str">
         <x:v>If the selected login name is already in use, the system does not create a second account with the same login.</x:v>
       </x:c>
-      <x:c r="F19" s="61" t="str">
+      <x:c r="F21" s="62" t="str">
         <x:v>Customer sees that the chosen user name is already in use and must choose another.</x:v>
       </x:c>
-      <x:c r="G19" s="61" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="H19" s="61" t="str">
+      <x:c r="G21" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H21" s="62" t="str">
         <x:v>CreateUserEJBAction.java; duplicate_account.jsp; mappings.xml</x:v>
       </x:c>
-      <x:c r="I19" s="61" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="J19" s="61" t="str">
+      <x:c r="I21" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J21" s="62" t="str">
         <x:v>Backend returns 409 for duplicate user id; UI shows a duplicate-account message and keeps the form state.</x:v>
       </x:c>
-      <x:c r="K19" s="61" t="str">
+      <x:c r="K21" s="62" t="str">
         <x:v>AccountController.cs; register.component.ts</x:v>
       </x:c>
-      <x:c r="L19" s="61" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="M19" s="61" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="N19" s="61" t="str">
+      <x:c r="L21" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M21" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N21" s="62" t="str">
         <x:v>specs/004-customer-accounts/spec.md FR-002; specs/005-account-ui/spec.md US2 scenario 2</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="66" customHeight="1">
-      <x:c r="A20" s="59" t="str">
-        <x:v>UF-002</x:v>
-      </x:c>
-      <x:c r="B20" s="59" t="str">
-        <x:v>New user account creation</x:v>
-      </x:c>
-      <x:c r="C20" s="60" t="str">
+    <x:row r="22" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A22" s="61" t="str"/>
+      <x:c r="B22" s="61" t="str"/>
+      <x:c r="C22" s="61" t="str">
         <x:v>Alternative path</x:v>
       </x:c>
-      <x:c r="D20" s="64" t="str">
+      <x:c r="D22" s="65" t="str">
         <x:v>Missing required customer profile/contact/payment fields are detected before customer data is built.</x:v>
       </x:c>
-      <x:c r="E20" s="64" t="str">
+      <x:c r="E22" s="65" t="str">
         <x:v>The system expects required customer information before creating a complete customer account. Missing required information should stop or block the account-details step.</x:v>
       </x:c>
-      <x:c r="F20" s="64" t="str">
+      <x:c r="F22" s="65" t="str">
         <x:v>Runtime feedback behavior needs confirmation; code detects missing fields, but the inspected flow does not show a dedicated friendly error for this exact case.</x:v>
       </x:c>
-      <x:c r="G20" s="64" t="str">
+      <x:c r="G22" s="65" t="str">
         <x:v>Partially</x:v>
       </x:c>
-      <x:c r="H20" s="64" t="str">
+      <x:c r="H22" s="65" t="str">
         <x:v>CustomerHTMLAction.java</x:v>
       </x:c>
-      <x:c r="I20" s="64" t="str">
+      <x:c r="I22" s="65" t="str">
         <x:v>Partially</x:v>
       </x:c>
-      <x:c r="J20" s="64" t="str">
+      <x:c r="J22" s="65" t="str">
         <x:v>Destination validates user id, password, and contact fields. Payment/profile fields are absent because they are deferred/out of scope.</x:v>
       </x:c>
-      <x:c r="K20" s="64" t="str">
+      <x:c r="K22" s="65" t="str">
         <x:v>AccountController.cs; ContactValidation.cs; register.component.ts</x:v>
       </x:c>
-      <x:c r="L20" s="64" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="M20" s="66" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="N20" s="64" t="str">
+      <x:c r="L22" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M22" s="67" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="N22" s="65" t="str">
         <x:v>specs/004-customer-accounts/spec.md FR-001 and US1 scenario 3; specs/004-customer-accounts/plan.md DD-003, DD-004</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="66" customHeight="1">
-      <x:c r="A21" s="59" t="str">
-        <x:v>UF-002</x:v>
-      </x:c>
-      <x:c r="B21" s="59" t="str">
-        <x:v>New user account creation</x:v>
-      </x:c>
-      <x:c r="C21" s="60" t="str">
+    <x:row r="23" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A23" s="61" t="str"/>
+      <x:c r="B23" s="61" t="str"/>
+      <x:c r="C23" s="61" t="str">
         <x:v>Gap / deferred</x:v>
       </x:c>
-      <x:c r="D21" s="64" t="str">
+      <x:c r="D23" s="65" t="str">
         <x:v>Repeated password field is shown but not enforced in the inspected account-creation action.</x:v>
       </x:c>
-      <x:c r="E21" s="64" t="str">
+      <x:c r="E23" s="65" t="str">
         <x:v>The legacy registration experience asks the customer to repeat the password, but the inspected behavior does not confirm that the two password values match before account creation.</x:v>
       </x:c>
-      <x:c r="F21" s="64" t="str">
+      <x:c r="F23" s="65" t="str">
         <x:v>Business rule should be decided for migration: either enforce matching passwords or remove the field.</x:v>
       </x:c>
-      <x:c r="G21" s="64" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="H21" s="64" t="str">
+      <x:c r="G23" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="H23" s="65" t="str">
         <x:v>signon.jsp; CreateUserHTMLAction.java</x:v>
       </x:c>
-      <x:c r="I21" s="64" t="str">
+      <x:c r="I23" s="65" t="str">
         <x:v>Not applicable</x:v>
       </x:c>
-      <x:c r="J21" s="64" t="str">
+      <x:c r="J23" s="65" t="str">
         <x:v>Destination registration has no repeated-password field, so the legacy bug is avoided by removing the field rather than validating it.</x:v>
       </x:c>
-      <x:c r="K21" s="64" t="str">
+      <x:c r="K23" s="65" t="str">
         <x:v>register.component.ts</x:v>
       </x:c>
-      <x:c r="L21" s="64" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="M21" s="64" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="N21" s="64" t="str">
+      <x:c r="L23" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="M23" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N23" s="65" t="str">
         <x:v>No password-repeat requirement or deferral found in specs/004-customer-accounts or specs/005-account-ui.</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="66" customHeight="1">
-      <x:c r="A22" s="59" t="str">
-        <x:v>UF-002</x:v>
-      </x:c>
-      <x:c r="B22" s="59" t="str">
-        <x:v>New user account creation</x:v>
-      </x:c>
-      <x:c r="C22" s="60" t="str">
+    <x:row r="24" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A24" s="61" t="str"/>
+      <x:c r="B24" s="61" t="str"/>
+      <x:c r="C24" s="61" t="str">
         <x:v>Gap / deferred</x:v>
       </x:c>
-      <x:c r="D22" s="57" t="str">
+      <x:c r="D24" s="57" t="str">
         <x:v>Account information step contains demo default values.</x:v>
       </x:c>
-      <x:c r="E22" s="57" t="str">
+      <x:c r="E24" s="57" t="str">
         <x:v>The legacy account-information step shows sample customer data by default. For a real customer-facing system, the expected behavior should be explicitly decided.</x:v>
       </x:c>
-      <x:c r="F22" s="57" t="str">
+      <x:c r="F24" s="57" t="str">
         <x:v>Migration should decide whether defaults are only demo data or should be removed for real users.</x:v>
       </x:c>
-      <x:c r="G22" s="57" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="H22" s="57" t="str">
+      <x:c r="G24" s="57" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H24" s="57" t="str">
         <x:v>create_customer.jsp</x:v>
       </x:c>
-      <x:c r="I22" s="57" t="str">
+      <x:c r="I24" s="57" t="str">
         <x:v>Not applicable</x:v>
       </x:c>
-      <x:c r="J22" s="57" t="str">
+      <x:c r="J24" s="57" t="str">
         <x:v>Destination registration form starts blank; no legacy demo contact/card defaults are shown.</x:v>
       </x:c>
-      <x:c r="K22" s="57" t="str">
+      <x:c r="K24" s="57" t="str">
         <x:v>register.component.ts</x:v>
       </x:c>
-      <x:c r="L22" s="57" t="str">
+      <x:c r="L24" s="57" t="str">
         <x:v>Partially</x:v>
       </x:c>
-      <x:c r="M22" s="57" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="N22" s="57" t="str">
+      <x:c r="M24" s="57" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N24" s="57" t="str">
         <x:v>specs/005-account-ui/spec.md FR-004 covers collecting registration fields; removing demo defaults is not called out explicitly.</x:v>
       </x:c>
     </x:row>
@@ -1375,15 +1379,6 @@
     <x:mergeCell ref="A5:H5"/>
     <x:mergeCell ref="I5:K5"/>
     <x:mergeCell ref="L5:N5"/>
-    <x:mergeCell ref="A7:A14"/>
-    <x:mergeCell ref="B7:B14"/>
-    <x:mergeCell ref="A15:A22"/>
-    <x:mergeCell ref="B15:B22"/>
-    <x:mergeCell ref="C7:C11"/>
-    <x:mergeCell ref="C12:C13"/>
-    <x:mergeCell ref="C15:C18"/>
-    <x:mergeCell ref="C19:C20"/>
-    <x:mergeCell ref="C21:C22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/analysis/petstore_legacy_user_flows_first_2.xlsx
+++ b/analysis/petstore_legacy_user_flows_first_2.xlsx
@@ -57,7 +57,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="16">
+  <x:fills count="17">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -134,6 +134,11 @@
         <x:fgColor rgb="FFF4B183"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFA9D18E"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -155,7 +160,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="69">
+  <x:cellXfs count="70">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -319,6 +324,9 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -522,7 +530,7 @@
 <file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User Flows" sheetId="1" r:id="R82b9c19f72924e70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User Flows" sheetId="1" r:id="Rfcdcc3351b074cac"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -552,7 +560,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="2" t="str">
-        <x:v>Legacy Petstore - First User Flows</x:v>
+        <x:v>Legacy Petstore - User Flows from Golden Code</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -718,7 +726,7 @@
         <x:v>Returning customer can start sign-in from the store experience or after requesting protected functionality.</x:v>
       </x:c>
       <x:c r="E8" s="62" t="str">
-        <x:v>The customer can start authentication from the normal store entry points or when they try to use functionality that requires identity. The same entry point also guides new customers toward account creation.</x:v>
+        <x:v>The customer can start authentication from normal store entry points or when the system needs identity before continuing.</x:v>
       </x:c>
       <x:c r="F8" s="62" t="str">
         <x:v>The user is asked for login and password and can choose to create a new account instead.</x:v>
@@ -733,7 +741,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="J8" s="62" t="str">
-        <x:v>Angular shell has a Sign in link; protected customer routes redirect anonymous users to /signin with returnUrl.</x:v>
+        <x:v>Angular shell exposes Sign in; protected customer routes redirect anonymous users to sign-in with returnUrl.</x:v>
       </x:c>
       <x:c r="K8" s="62" t="str">
         <x:v>catalog-shell.component.ts; auth.guard.ts; app.routes.ts</x:v>
@@ -758,7 +766,7 @@
         <x:v>System validates the submitted user name and password against registered users.</x:v>
       </x:c>
       <x:c r="E9" s="62" t="str">
-        <x:v>When the customer submits login details, the system checks that the account exists and that the password is correct.</x:v>
+        <x:v>When the customer submits credentials, the system checks that the account exists and the password is correct.</x:v>
       </x:c>
       <x:c r="F9" s="62" t="str">
         <x:v>Valid credentials are accepted; invalid credentials are rejected.</x:v>
@@ -795,10 +803,10 @@
         <x:v>Happy path</x:v>
       </x:c>
       <x:c r="D10" s="62" t="str">
-        <x:v>Successful login creates a signed-in session for the user.</x:v>
+        <x:v>Successful login creates a signed-in state for later customer actions.</x:v>
       </x:c>
       <x:c r="E10" s="62" t="str">
-        <x:v>After a successful sign-in, the store recognizes the customer as signed in for subsequent account, checkout, and order actions.</x:v>
+        <x:v>After successful sign-in, the store recognizes the customer for account, checkout, and order actions.</x:v>
       </x:c>
       <x:c r="F10" s="62" t="str">
         <x:v>The system shows the customer as signed in and protected functionality becomes accessible.</x:v>
@@ -813,7 +821,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="J10" s="62" t="str">
-        <x:v>Destination uses JWT identity in Angular instead of a legacy server session; header shows user id and Sign out while signed in.</x:v>
+        <x:v>Destination uses JWT identity instead of a server session; the shell shows user id and sign-out while signed in.</x:v>
       </x:c>
       <x:c r="K10" s="62" t="str">
         <x:v>identity.service.ts; catalog-shell.component.ts; auth.interceptor.ts</x:v>
@@ -838,10 +846,10 @@
         <x:v>Successful login returns the customer to the functionality they originally requested.</x:v>
       </x:c>
       <x:c r="E11" s="62" t="str">
-        <x:v>If the customer was asked to sign in before using protected functionality, the system remembers the intended destination and continues there after successful sign-in.</x:v>
+        <x:v>If the customer was asked to sign in before using protected functionality, the system remembers the intended destination.</x:v>
       </x:c>
       <x:c r="F11" s="62" t="str">
-        <x:v>The customer continues to the originally requested capability instead of a generic success destination.</x:v>
+        <x:v>The customer continues to the originally requested capability instead of a generic destination.</x:v>
       </x:c>
       <x:c r="G11" s="62" t="str">
         <x:v>Yes</x:v>
@@ -853,7 +861,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="J11" s="62" t="str">
-        <x:v>authGuard stores the requested route as returnUrl; SignInComponent navigates back to it after successful sign-in.</x:v>
+        <x:v>authGuard stores returnUrl; SignInComponent navigates back after successful sign-in.</x:v>
       </x:c>
       <x:c r="K11" s="62" t="str">
         <x:v>auth.guard.ts; sign-in.component.ts</x:v>
@@ -878,10 +886,10 @@
         <x:v>Remember user name stores only the login name for future convenience.</x:v>
       </x:c>
       <x:c r="E12" s="64" t="str">
-        <x:v>If the user chooses to be remembered, the system pre-fills the last used login name the next time authentication is requested. The password is still required.</x:v>
+        <x:v>If the user chooses to be remembered, the next authentication request pre-fills the last used login name. The password is still required.</x:v>
       </x:c>
       <x:c r="F12" s="64" t="str">
-        <x:v>Next visit pre-fills the user name; password field remains separate.</x:v>
+        <x:v>Next visit pre-fills the user name; password remains separate.</x:v>
       </x:c>
       <x:c r="G12" s="64" t="str">
         <x:v>Yes</x:v>
@@ -893,7 +901,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="J12" s="64" t="str">
-        <x:v>No remember-user-name checkbox/cookie exists in the Angular sign-in flow. The destination stores JWT identity for session restore, not a username convenience cookie.</x:v>
+        <x:v>No remember-user-name checkbox/cookie exists. Destination restores signed-in identity from JWT, not a username convenience value.</x:v>
       </x:c>
       <x:c r="K12" s="64" t="str">
         <x:v>sign-in.component.ts; identity.service.ts</x:v>
@@ -918,10 +926,10 @@
         <x:v>Invalid user name or password shows a sign-in error.</x:v>
       </x:c>
       <x:c r="E13" s="62" t="str">
-        <x:v>If the login name or password is incorrect, the system rejects the sign-in attempt without signing in the customer.</x:v>
+        <x:v>If the login name or password is incorrect, the system rejects sign-in without revealing which value was wrong.</x:v>
       </x:c>
       <x:c r="F13" s="62" t="str">
-        <x:v>Customer sees a Sign-in Error message and is told to try again.</x:v>
+        <x:v>Customer sees a sign-in error and remains signed out.</x:v>
       </x:c>
       <x:c r="G13" s="62" t="str">
         <x:v>Yes</x:v>
@@ -933,7 +941,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="J13" s="62" t="str">
-        <x:v>Backend returns the same invalid-credentials response for wrong password/unknown user; UI shows a generic error and clears the password.</x:v>
+        <x:v>Backend returns identical invalid-credentials responses for unknown users and wrong passwords; UI shows a generic error.</x:v>
       </x:c>
       <x:c r="K13" s="62" t="str">
         <x:v>AuthController.cs; sign-in.component.ts</x:v>
@@ -958,10 +966,10 @@
         <x:v>Protected functionality requires login before access.</x:v>
       </x:c>
       <x:c r="E14" s="62" t="str">
-        <x:v>When a signed-out customer tries to use account, checkout, order, or other protected functionality, the system asks for login and password before continuing.</x:v>
+        <x:v>When a signed-out customer tries to use account, checkout, or order functionality, the system asks for credentials first.</x:v>
       </x:c>
       <x:c r="F14" s="62" t="str">
-        <x:v>The customer cannot continue to protected functionality until login succeeds.</x:v>
+        <x:v>The customer cannot continue until login succeeds.</x:v>
       </x:c>
       <x:c r="G14" s="62" t="str">
         <x:v>Yes</x:v>
@@ -973,10 +981,10 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="J14" s="62" t="str">
-        <x:v>Angular guards protect account, checkout, and order routes; backend authenticated account/order APIs also require authorization.</x:v>
+        <x:v>Angular guards protect account, checkout, and order routes; backend account/order APIs require authorization.</x:v>
       </x:c>
       <x:c r="K14" s="62" t="str">
-        <x:v>auth.guard.ts; app.routes.ts; AccountController.cs; OrdersController.cs</x:v>
+        <x:v>auth.guard.ts; AccountController.cs; OrdersController.cs; app.routes.ts</x:v>
       </x:c>
       <x:c r="L14" s="62" t="str">
         <x:v>Yes</x:v>
@@ -985,23 +993,23 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="N14" s="62" t="str">
-        <x:v>specs/005-account-ui/spec.md FR-006; specs/008-checkout-orders/spec.md checkout requires signed-in customer</x:v>
+        <x:v>specs/005-account-ui/spec.md FR-006; specs/008-checkout-orders/spec.md FR-007</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="66" customHeight="1" outlineLevel="1" hidden="1">
       <x:c r="A15" s="61" t="str"/>
       <x:c r="B15" s="61" t="str"/>
       <x:c r="C15" s="61" t="str">
-        <x:v>Gap / deferred</x:v>
+        <x:v>Review</x:v>
       </x:c>
       <x:c r="D15" s="65" t="str">
-        <x:v>Direct sign-in does not define a clear post-login destination in the inspected legacy code.</x:v>
+        <x:v>Direct sign-in has an expected default destination.</x:v>
       </x:c>
       <x:c r="E15" s="65" t="str">
-        <x:v>When sign-in is started directly rather than as part of a protected action, the expected destination after successful sign-in is not clearly defined in the legacy behavior.</x:v>
+        <x:v>When sign-in starts directly, the system should have a clear place to send the customer after success.</x:v>
       </x:c>
       <x:c r="F15" s="65" t="str">
-        <x:v>Needs confirmation in runtime or migration design: expected default destination after direct login.</x:v>
+        <x:v>Direct sign-in lands in a predictable store experience.</x:v>
       </x:c>
       <x:c r="G15" s="65" t="str">
         <x:v>Partially</x:v>
@@ -1013,7 +1021,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="J15" s="65" t="str">
-        <x:v>Direct /signin without returnUrl lands on /catalog after success, so destination has a defined default.</x:v>
+        <x:v>Destination defines a default /catalog landing when no returnUrl is present.</x:v>
       </x:c>
       <x:c r="K15" s="65" t="str">
         <x:v>sign-in.component.ts</x:v>
@@ -1025,7 +1033,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="N15" s="65" t="str">
-        <x:v>specs/005-account-ui/plan.md DD-003 covers returnUrl; default /catalog landing is not called out explicitly.</x:v>
+        <x:v>specs/005-account-ui/plan.md DD-003 covers returnUrl; default landing is implementation behavior, not explicit SDD text.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="37.5" customHeight="1" collapsed="1">
@@ -1062,7 +1070,7 @@
         <x:v>New customer can start account creation from the sign-in experience.</x:v>
       </x:c>
       <x:c r="E17" s="62" t="str">
-        <x:v>A new customer can start registration from the sign-in experience by choosing to create an account.</x:v>
+        <x:v>A new customer can start registration by choosing to create an account from the sign-in experience.</x:v>
       </x:c>
       <x:c r="F17" s="62" t="str">
         <x:v>Customer can submit Create New Account.</x:v>
@@ -1077,7 +1085,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="J17" s="62" t="str">
-        <x:v>The sign-in view links to a separate /register route instead of embedding registration on the same page.</x:v>
+        <x:v>The sign-in view links to a separate /register route.</x:v>
       </x:c>
       <x:c r="K17" s="62" t="str">
         <x:v>sign-in.component.ts; register.component.ts; app.routes.ts</x:v>
@@ -1102,10 +1110,10 @@
         <x:v>Application creates a login record for a new user name and password.</x:v>
       </x:c>
       <x:c r="E18" s="62" t="str">
-        <x:v>After the user provides a new login name and password, the system creates the account identity used for the rest of registration.</x:v>
+        <x:v>After the user provides a new login name and password, the system creates the account identity used for registration.</x:v>
       </x:c>
       <x:c r="F18" s="62" t="str">
-        <x:v>Customer proceeds to provide account information.</x:v>
+        <x:v>Customer proceeds with a stored login identity.</x:v>
       </x:c>
       <x:c r="G18" s="62" t="str">
         <x:v>Yes</x:v>
@@ -1117,7 +1125,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="J18" s="62" t="str">
-        <x:v>RegisterComponent posts user id/password/contact to POST /api/account; backend creates the user with hashed password.</x:v>
+        <x:v>RegisterComponent posts user id/password/contact; backend creates a user with hashed password.</x:v>
       </x:c>
       <x:c r="K18" s="62" t="str">
         <x:v>register.component.ts; AccountController.cs; AccountRepository.cs</x:v>
@@ -1142,7 +1150,7 @@
         <x:v>Customer enters account profile, contact, credit card, language, and preference information.</x:v>
       </x:c>
       <x:c r="E19" s="65" t="str">
-        <x:v>The customer provides the account details needed by the legacy store, including contact details, payment information, language, favorite category, and personalization preferences.</x:v>
+        <x:v>The legacy account form collects contact details, payment information, language, favorite category, and personalization preferences.</x:v>
       </x:c>
       <x:c r="F19" s="65" t="str">
         <x:v>Customer can submit the complete account profile.</x:v>
@@ -1157,7 +1165,7 @@
         <x:v>Partially</x:v>
       </x:c>
       <x:c r="J19" s="65" t="str">
-        <x:v>Destination registration collects contact info, but not credit card, language, favorite category, MyList, or banner preferences.</x:v>
+        <x:v>Destination registration collects user id, password, and contact info, but not credit card, language, favorite category, MyList, or banner preferences.</x:v>
       </x:c>
       <x:c r="K19" s="65" t="str">
         <x:v>register.component.ts; RegisterRequestDto.cs; AccountController.cs</x:v>
@@ -1169,7 +1177,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="N19" s="65" t="str">
-        <x:v>specs/004-customer-accounts/plan.md DD-003 no credit card storage, DD-004 profile preferences deferred; specs/005-account-ui/spec.md assumptions</x:v>
+        <x:v>specs/004-customer-accounts/plan.md DD-003 no credit card storage; DD-004 profile preferences deferred; specs/005-account-ui/spec.md assumptions</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="66" customHeight="1" outlineLevel="1" hidden="1">
@@ -1182,10 +1190,10 @@
         <x:v>After profile submission, the system creates/updates customer data and signs the customer in.</x:v>
       </x:c>
       <x:c r="E20" s="65" t="str">
-        <x:v>After the customer submits account details, the system saves the customer profile and treats the customer as signed in.</x:v>
+        <x:v>After account details are submitted, the system saves the customer profile and treats the customer as signed in.</x:v>
       </x:c>
       <x:c r="F20" s="65" t="str">
-        <x:v>The system shows the customer as signed in; account and checkout flows are available as authenticated functionality.</x:v>
+        <x:v>The system shows the customer as signed in; protected functionality becomes available.</x:v>
       </x:c>
       <x:c r="G20" s="65" t="str">
         <x:v>Yes</x:v>
@@ -1197,7 +1205,7 @@
         <x:v>Partially</x:v>
       </x:c>
       <x:c r="J20" s="65" t="str">
-        <x:v>Destination creates account/contact and auto signs in, but payment/profile/preferences/locale are not part of account creation.</x:v>
+        <x:v>Destination creates account/contact and signs the user in, but deferred payment/profile/preference data is not created.</x:v>
       </x:c>
       <x:c r="K20" s="65" t="str">
         <x:v>AccountController.cs; register.component.ts; identity.service.ts</x:v>
@@ -1209,7 +1217,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="N20" s="65" t="str">
-        <x:v>specs/005-account-ui/plan.md DD-004 auto sign-in; specs/004-customer-accounts/plan.md DD-003, DD-004 defer payment/profile data</x:v>
+        <x:v>specs/005-account-ui/plan.md DD-004; specs/004-customer-accounts/plan.md DD-003, DD-004</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="66" customHeight="1" outlineLevel="1" hidden="1">
@@ -1237,7 +1245,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="J21" s="62" t="str">
-        <x:v>Backend returns 409 for duplicate user id; UI shows a duplicate-account message and keeps the form state.</x:v>
+        <x:v>Backend returns 409 for duplicate user id; UI shows a duplicate-account message.</x:v>
       </x:c>
       <x:c r="K21" s="62" t="str">
         <x:v>AccountController.cs; register.component.ts</x:v>
@@ -1262,10 +1270,10 @@
         <x:v>Missing required customer profile/contact/payment fields are detected before customer data is built.</x:v>
       </x:c>
       <x:c r="E22" s="65" t="str">
-        <x:v>The system expects required customer information before creating a complete customer account. Missing required information should stop or block the account-details step.</x:v>
+        <x:v>The system expects required customer information before creating a complete customer account.</x:v>
       </x:c>
       <x:c r="F22" s="65" t="str">
-        <x:v>Runtime feedback behavior needs confirmation; code detects missing fields, but the inspected flow does not show a dedicated friendly error for this exact case.</x:v>
+        <x:v>Missing required information stops or blocks the account-details step.</x:v>
       </x:c>
       <x:c r="G22" s="65" t="str">
         <x:v>Partially</x:v>
@@ -1277,7 +1285,7 @@
         <x:v>Partially</x:v>
       </x:c>
       <x:c r="J22" s="65" t="str">
-        <x:v>Destination validates user id, password, and contact fields. Payment/profile fields are absent because they are deferred/out of scope.</x:v>
+        <x:v>Destination validates user id, password, and contact fields. Payment/profile fields are absent because they are deferred or out of scope.</x:v>
       </x:c>
       <x:c r="K22" s="65" t="str">
         <x:v>AccountController.cs; ContactValidation.cs; register.component.ts</x:v>
@@ -1289,23 +1297,23 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="N22" s="65" t="str">
-        <x:v>specs/004-customer-accounts/spec.md FR-001 and US1 scenario 3; specs/004-customer-accounts/plan.md DD-003, DD-004</x:v>
+        <x:v>specs/004-customer-accounts/spec.md FR-001; specs/004-customer-accounts/plan.md DD-003, DD-004</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="66" customHeight="1" outlineLevel="1" hidden="1">
       <x:c r="A23" s="61" t="str"/>
       <x:c r="B23" s="61" t="str"/>
       <x:c r="C23" s="61" t="str">
-        <x:v>Gap / deferred</x:v>
+        <x:v>Legacy gap</x:v>
       </x:c>
       <x:c r="D23" s="65" t="str">
         <x:v>Repeated password field is shown but not enforced in the inspected account-creation action.</x:v>
       </x:c>
       <x:c r="E23" s="65" t="str">
-        <x:v>The legacy registration experience asks the customer to repeat the password, but the inspected behavior does not confirm that the two password values match before account creation.</x:v>
+        <x:v>The legacy registration experience asks the customer to repeat the password, but the inspected action does not compare both values.</x:v>
       </x:c>
       <x:c r="F23" s="65" t="str">
-        <x:v>Business rule should be decided for migration: either enforce matching passwords or remove the field.</x:v>
+        <x:v>Business rule should be decided: enforce matching passwords or remove the field.</x:v>
       </x:c>
       <x:c r="G23" s="65" t="str">
         <x:v>No</x:v>
@@ -1317,7 +1325,7 @@
         <x:v>Not applicable</x:v>
       </x:c>
       <x:c r="J23" s="65" t="str">
-        <x:v>Destination registration has no repeated-password field, so the legacy bug is avoided by removing the field rather than validating it.</x:v>
+        <x:v>Destination registration has no repeated-password field, so the legacy bug is avoided by removing the field.</x:v>
       </x:c>
       <x:c r="K23" s="65" t="str">
         <x:v>register.component.ts</x:v>
@@ -1336,40 +1344,3312 @@
       <x:c r="A24" s="61" t="str"/>
       <x:c r="B24" s="61" t="str"/>
       <x:c r="C24" s="61" t="str">
-        <x:v>Gap / deferred</x:v>
-      </x:c>
-      <x:c r="D24" s="57" t="str">
-        <x:v>Account information step contains demo default values.</x:v>
-      </x:c>
-      <x:c r="E24" s="57" t="str">
-        <x:v>The legacy account-information step shows sample customer data by default. For a real customer-facing system, the expected behavior should be explicitly decided.</x:v>
-      </x:c>
-      <x:c r="F24" s="57" t="str">
-        <x:v>Migration should decide whether defaults are only demo data or should be removed for real users.</x:v>
-      </x:c>
-      <x:c r="G24" s="57" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="H24" s="57" t="str">
+        <x:v>Legacy gap</x:v>
+      </x:c>
+      <x:c r="D24" s="65" t="str">
+        <x:v>Account information form contains demo default values.</x:v>
+      </x:c>
+      <x:c r="E24" s="65" t="str">
+        <x:v>The legacy account-information step shows sample customer data by default.</x:v>
+      </x:c>
+      <x:c r="F24" s="65" t="str">
+        <x:v>Migration should decide whether defaults are demo-only or should be removed for real users.</x:v>
+      </x:c>
+      <x:c r="G24" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H24" s="65" t="str">
         <x:v>create_customer.jsp</x:v>
       </x:c>
-      <x:c r="I24" s="57" t="str">
+      <x:c r="I24" s="65" t="str">
         <x:v>Not applicable</x:v>
       </x:c>
-      <x:c r="J24" s="57" t="str">
-        <x:v>Destination registration form starts blank; no legacy demo contact/card defaults are shown.</x:v>
-      </x:c>
-      <x:c r="K24" s="57" t="str">
+      <x:c r="J24" s="65" t="str">
+        <x:v>Destination registration starts blank and does not show legacy demo contact/card defaults.</x:v>
+      </x:c>
+      <x:c r="K24" s="65" t="str">
         <x:v>register.component.ts</x:v>
       </x:c>
-      <x:c r="L24" s="57" t="str">
+      <x:c r="L24" s="65" t="str">
         <x:v>Partially</x:v>
       </x:c>
-      <x:c r="M24" s="57" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="N24" s="57" t="str">
-        <x:v>specs/005-account-ui/spec.md FR-004 covers collecting registration fields; removing demo defaults is not called out explicitly.</x:v>
+      <x:c r="M24" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N24" s="65" t="str">
+        <x:v>specs/005-account-ui/spec.md FR-004 covers collecting fields; removing demo defaults is not explicitly called out.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="37.5" customHeight="1" collapsed="1">
+      <x:c r="A25" s="67" t="str">
+        <x:v>UF-003</x:v>
+      </x:c>
+      <x:c r="B25" s="67" t="str">
+        <x:v>Browse product catalog</x:v>
+      </x:c>
+      <x:c r="C25" s="67" t="str">
+        <x:v>Not Passed - Deferred/Partial</x:v>
+      </x:c>
+      <x:c r="D25" s="67" t="str">
+        <x:v>At least one requirement is partial, deferred, or a known gap.</x:v>
+      </x:c>
+      <x:c r="E25" s="67" t="str"/>
+      <x:c r="F25" s="67" t="str"/>
+      <x:c r="G25" s="67" t="str"/>
+      <x:c r="H25" s="67" t="str"/>
+      <x:c r="I25" s="67" t="str"/>
+      <x:c r="J25" s="67" t="str"/>
+      <x:c r="K25" s="67" t="str"/>
+      <x:c r="L25" s="67" t="str"/>
+      <x:c r="M25" s="67" t="str"/>
+      <x:c r="N25" s="67" t="str"/>
+    </x:row>
+    <x:row r="26" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A26" s="61" t="str"/>
+      <x:c r="B26" s="61" t="str"/>
+      <x:c r="C26" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D26" s="62" t="str">
+        <x:v>Visitor can browse catalog categories without signing in.</x:v>
+      </x:c>
+      <x:c r="E26" s="62" t="str">
+        <x:v>The store exposes the main catalog categories for ordinary browsing before authentication.</x:v>
+      </x:c>
+      <x:c r="F26" s="62" t="str">
+        <x:v>Visitor sees Fish, Dogs, Reptiles, Cats, and Birds categories.</x:v>
+      </x:c>
+      <x:c r="G26" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H26" s="62" t="str">
+        <x:v>main.jsp; sidebar.jsp; CatalogEJB.java</x:v>
+      </x:c>
+      <x:c r="I26" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J26" s="62" t="str">
+        <x:v>Angular catalog home lists categories from the backend API without auth.</x:v>
+      </x:c>
+      <x:c r="K26" s="62" t="str">
+        <x:v>CategoryListComponent.ts; CatalogCategoriesController.cs; app.routes.ts</x:v>
+      </x:c>
+      <x:c r="L26" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M26" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N26" s="62" t="str">
+        <x:v>specs/002-browse-product-catalog/spec.md FR-001, FR-003, FR-016; specs/003-catalog-angular-ui/spec.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A27" s="61" t="str"/>
+      <x:c r="B27" s="61" t="str"/>
+      <x:c r="C27" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D27" s="62" t="str">
+        <x:v>Visitor can open a category and see products in that category.</x:v>
+      </x:c>
+      <x:c r="E27" s="62" t="str">
+        <x:v>Selecting a category returns the product families that belong to it.</x:v>
+      </x:c>
+      <x:c r="F27" s="62" t="str">
+        <x:v>Products are shown with names/descriptions and can be opened.</x:v>
+      </x:c>
+      <x:c r="G27" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H27" s="62" t="str">
+        <x:v>category.jsp; CatalogHelper.java; CatalogEJB.java</x:v>
+      </x:c>
+      <x:c r="I27" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J27" s="62" t="str">
+        <x:v>Destination exposes category products and renders them in the Angular catalog.</x:v>
+      </x:c>
+      <x:c r="K27" s="62" t="str">
+        <x:v>CatalogCategoriesController.cs; ProductListComponent.ts; CatalogRepository.cs</x:v>
+      </x:c>
+      <x:c r="L27" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M27" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N27" s="62" t="str">
+        <x:v>specs/002-browse-product-catalog/spec.md FR-004, FR-008, FR-009</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A28" s="61" t="str"/>
+      <x:c r="B28" s="61" t="str"/>
+      <x:c r="C28" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D28" s="62" t="str">
+        <x:v>Visitor can open a product and see sellable items.</x:v>
+      </x:c>
+      <x:c r="E28" s="62" t="str">
+        <x:v>Selecting a product shows the specific sellable items with stable item ids.</x:v>
+      </x:c>
+      <x:c r="F28" s="62" t="str">
+        <x:v>Items are shown with id, name, price, and navigation to details.</x:v>
+      </x:c>
+      <x:c r="G28" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H28" s="62" t="str">
+        <x:v>product.jsp; CatalogHelper.java; CatalogEJB.java</x:v>
+      </x:c>
+      <x:c r="I28" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J28" s="62" t="str">
+        <x:v>Destination exposes product items and renders item lists.</x:v>
+      </x:c>
+      <x:c r="K28" s="62" t="str">
+        <x:v>CatalogProductsController.cs; ItemListComponent.ts</x:v>
+      </x:c>
+      <x:c r="L28" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M28" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N28" s="62" t="str">
+        <x:v>specs/002-browse-product-catalog/spec.md FR-005, FR-010, FR-011, FR-012</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A29" s="61" t="str"/>
+      <x:c r="B29" s="61" t="str"/>
+      <x:c r="C29" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D29" s="62" t="str">
+        <x:v>Visitor can open item details and add the item to the cart.</x:v>
+      </x:c>
+      <x:c r="E29" s="62" t="str">
+        <x:v>A sellable item has details and an add-to-cart action from item views.</x:v>
+      </x:c>
+      <x:c r="F29" s="62" t="str">
+        <x:v>Customer can inspect item information and start a cart line.</x:v>
+      </x:c>
+      <x:c r="G29" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H29" s="62" t="str">
+        <x:v>item.jsp; product.jsp; cart.do</x:v>
+      </x:c>
+      <x:c r="I29" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J29" s="62" t="str">
+        <x:v>Item list and detail views both have add-to-cart actions backed by the cart API.</x:v>
+      </x:c>
+      <x:c r="K29" s="62" t="str">
+        <x:v>ItemListComponent.ts; ItemDetailComponent.ts; CartController.cs</x:v>
+      </x:c>
+      <x:c r="L29" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M29" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N29" s="62" t="str">
+        <x:v>specs/002-browse-product-catalog/spec.md FR-006, FR-012; specs/007-cart-ui/spec.md FR-001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A30" s="61" t="str"/>
+      <x:c r="B30" s="61" t="str"/>
+      <x:c r="C30" s="61" t="str">
+        <x:v>Alternative path</x:v>
+      </x:c>
+      <x:c r="D30" s="65" t="str">
+        <x:v>Missing category, product, or item produces a clear not-found or empty result.</x:v>
+      </x:c>
+      <x:c r="E30" s="65" t="str">
+        <x:v>If the requested catalog object does not exist, the system should not silently show the wrong data.</x:v>
+      </x:c>
+      <x:c r="F30" s="65" t="str">
+        <x:v>Visitor sees a clear missing/empty state.</x:v>
+      </x:c>
+      <x:c r="G30" s="65" t="str">
+        <x:v>Partially</x:v>
+      </x:c>
+      <x:c r="H30" s="65" t="str">
+        <x:v>CatalogDAO.java; category.jsp; product.jsp; item.jsp</x:v>
+      </x:c>
+      <x:c r="I30" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J30" s="65" t="str">
+        <x:v>Backend returns 404 for missing category/product/item; Angular renders not-found states.</x:v>
+      </x:c>
+      <x:c r="K30" s="65" t="str">
+        <x:v>CatalogCategoriesController.cs; CatalogProductsController.cs; CatalogItemsController.cs; ProductListComponent.ts; ItemDetailComponent.ts</x:v>
+      </x:c>
+      <x:c r="L30" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M30" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N30" s="65" t="str">
+        <x:v>specs/002-browse-product-catalog/spec.md FR-014</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A31" s="61" t="str"/>
+      <x:c r="B31" s="61" t="str"/>
+      <x:c r="C31" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D31" s="62" t="str">
+        <x:v>Catalog preserves stable legacy ids for categories, products, and items.</x:v>
+      </x:c>
+      <x:c r="E31" s="62" t="str">
+        <x:v>Downstream cart and order flows depend on the same stable identifiers from catalog data.</x:v>
+      </x:c>
+      <x:c r="F31" s="62" t="str">
+        <x:v>Selected item ids can be used later by cart and order placement.</x:v>
+      </x:c>
+      <x:c r="G31" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H31" s="62" t="str">
+        <x:v>Populate-UTF8.xml; CatalogDAOSQL.xml; CatalogEJB.java</x:v>
+      </x:c>
+      <x:c r="I31" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J31" s="62" t="str">
+        <x:v>Destination seeds the English legacy catalog and preserves stable ids.</x:v>
+      </x:c>
+      <x:c r="K31" s="62" t="str">
+        <x:v>CatalogSeeder.cs; FullLegacyCatalogSeed migration; CatalogRepository.cs</x:v>
+      </x:c>
+      <x:c r="L31" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M31" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N31" s="62" t="str">
+        <x:v>specs/002-browse-product-catalog/spec.md FR-013, FR-020, FR-022</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="37.5" customHeight="1" collapsed="1">
+      <x:c r="A32" s="67" t="str">
+        <x:v>UF-004</x:v>
+      </x:c>
+      <x:c r="B32" s="67" t="str">
+        <x:v>Search catalog</x:v>
+      </x:c>
+      <x:c r="C32" s="67" t="str">
+        <x:v>Not Passed - Deferred/Partial</x:v>
+      </x:c>
+      <x:c r="D32" s="67" t="str">
+        <x:v>At least one requirement is partial, deferred, or a known gap.</x:v>
+      </x:c>
+      <x:c r="E32" s="67" t="str"/>
+      <x:c r="F32" s="67" t="str"/>
+      <x:c r="G32" s="67" t="str"/>
+      <x:c r="H32" s="67" t="str"/>
+      <x:c r="I32" s="67" t="str"/>
+      <x:c r="J32" s="67" t="str"/>
+      <x:c r="K32" s="67" t="str"/>
+      <x:c r="L32" s="67" t="str"/>
+      <x:c r="M32" s="67" t="str"/>
+      <x:c r="N32" s="67" t="str"/>
+    </x:row>
+    <x:row r="33" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A33" s="61" t="str"/>
+      <x:c r="B33" s="61" t="str"/>
+      <x:c r="C33" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D33" s="65" t="str">
+        <x:v>Visitor can search catalog items from the store experience.</x:v>
+      </x:c>
+      <x:c r="E33" s="65" t="str">
+        <x:v>The legacy store accepts keywords and searches items by query.</x:v>
+      </x:c>
+      <x:c r="F33" s="65" t="str">
+        <x:v>Matching items are listed for the visitor.</x:v>
+      </x:c>
+      <x:c r="G33" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H33" s="65" t="str">
+        <x:v>banner.jsp; search.jsp; CatalogHelper.java; CatalogEJB.searchItems</x:v>
+      </x:c>
+      <x:c r="I33" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="J33" s="65" t="str">
+        <x:v>No catalog search route, API method, or Angular search experience exists in destination.</x:v>
+      </x:c>
+      <x:c r="K33" s="65" t="str">
+        <x:v>CatalogApiService.ts; Catalog*Controller.cs; app.routes.ts</x:v>
+      </x:c>
+      <x:c r="L33" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M33" s="67" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="N33" s="65" t="str">
+        <x:v>specs/002-browse-product-catalog/spec.md notes search outside first slice; specs/002-browse-product-catalog/plan.md constraints</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A34" s="61" t="str"/>
+      <x:c r="B34" s="61" t="str"/>
+      <x:c r="C34" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D34" s="65" t="str">
+        <x:v>Search results can be opened as item details.</x:v>
+      </x:c>
+      <x:c r="E34" s="65" t="str">
+        <x:v>A search result is a usable catalog item, not just text.</x:v>
+      </x:c>
+      <x:c r="F34" s="65" t="str">
+        <x:v>Visitor can open an item and continue shopping.</x:v>
+      </x:c>
+      <x:c r="G34" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H34" s="65" t="str">
+        <x:v>search.jsp; item.screen</x:v>
+      </x:c>
+      <x:c r="I34" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="J34" s="65" t="str">
+        <x:v>Destination lacks search results; item detail itself exists once reached by direct item route.</x:v>
+      </x:c>
+      <x:c r="K34" s="65" t="str">
+        <x:v>ItemDetailComponent.ts; CatalogItemsController.cs</x:v>
+      </x:c>
+      <x:c r="L34" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M34" s="67" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="N34" s="65" t="str">
+        <x:v>specs/002-browse-product-catalog/spec.md search out of scope</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A35" s="61" t="str"/>
+      <x:c r="B35" s="61" t="str"/>
+      <x:c r="C35" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D35" s="65" t="str">
+        <x:v>Search results can add items to the cart.</x:v>
+      </x:c>
+      <x:c r="E35" s="65" t="str">
+        <x:v>The legacy search result includes a purchase action for each item.</x:v>
+      </x:c>
+      <x:c r="F35" s="65" t="str">
+        <x:v>Visitor can add a searched item to the cart directly.</x:v>
+      </x:c>
+      <x:c r="G35" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H35" s="65" t="str">
+        <x:v>search.jsp; cart.do action=purchase</x:v>
+      </x:c>
+      <x:c r="I35" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="J35" s="65" t="str">
+        <x:v>Destination add-to-cart exists on item lists/details, but there is no search result surface.</x:v>
+      </x:c>
+      <x:c r="K35" s="65" t="str">
+        <x:v>ItemListComponent.ts; ItemDetailComponent.ts; CartService.ts</x:v>
+      </x:c>
+      <x:c r="L35" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M35" s="67" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="N35" s="65" t="str">
+        <x:v>specs/002-browse-product-catalog/spec.md search out of scope; specs/007-cart-ui/spec.md add-to-cart surfaces</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A36" s="61" t="str"/>
+      <x:c r="B36" s="61" t="str"/>
+      <x:c r="C36" s="61" t="str">
+        <x:v>Alternative path</x:v>
+      </x:c>
+      <x:c r="D36" s="65" t="str">
+        <x:v>Search supports paging through result sets.</x:v>
+      </x:c>
+      <x:c r="E36" s="65" t="str">
+        <x:v>Legacy search uses start/count and previous/next links for multiple results.</x:v>
+      </x:c>
+      <x:c r="F36" s="65" t="str">
+        <x:v>Visitor can continue through more matches without losing the query.</x:v>
+      </x:c>
+      <x:c r="G36" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H36" s="65" t="str">
+        <x:v>search.jsp; CatalogHelper.setStart; Page.java</x:v>
+      </x:c>
+      <x:c r="I36" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="J36" s="65" t="str">
+        <x:v>Destination has no search feature or search pagination.</x:v>
+      </x:c>
+      <x:c r="K36" s="65" t="str">
+        <x:v>CatalogApiService.ts; app.routes.ts</x:v>
+      </x:c>
+      <x:c r="L36" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M36" s="67" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="N36" s="65" t="str">
+        <x:v>specs/002-browse-product-catalog/spec.md search out of scope</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="37.5" customHeight="1" collapsed="1">
+      <x:c r="A37" s="67" t="str">
+        <x:v>UF-005</x:v>
+      </x:c>
+      <x:c r="B37" s="67" t="str">
+        <x:v>Personalization and localization</x:v>
+      </x:c>
+      <x:c r="C37" s="67" t="str">
+        <x:v>Not Passed - Deferred/Partial</x:v>
+      </x:c>
+      <x:c r="D37" s="67" t="str">
+        <x:v>At least one requirement is partial, deferred, or a known gap.</x:v>
+      </x:c>
+      <x:c r="E37" s="67" t="str"/>
+      <x:c r="F37" s="67" t="str"/>
+      <x:c r="G37" s="67" t="str"/>
+      <x:c r="H37" s="67" t="str"/>
+      <x:c r="I37" s="67" t="str"/>
+      <x:c r="J37" s="67" t="str"/>
+      <x:c r="K37" s="67" t="str"/>
+      <x:c r="L37" s="67" t="str"/>
+      <x:c r="M37" s="67" t="str"/>
+      <x:c r="N37" s="67" t="str"/>
+    </x:row>
+    <x:row r="38" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A38" s="61" t="str"/>
+      <x:c r="B38" s="61" t="str"/>
+      <x:c r="C38" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D38" s="65" t="str">
+        <x:v>Customer can choose a preferred language.</x:v>
+      </x:c>
+      <x:c r="E38" s="65" t="str">
+        <x:v>The legacy account profile stores a preferred language and the store can switch locale.</x:v>
+      </x:c>
+      <x:c r="F38" s="65" t="str">
+        <x:v>Catalog/account text and selected profile language can follow the preference.</x:v>
+      </x:c>
+      <x:c r="G38" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H38" s="65" t="str">
+        <x:v>banner.jsp; changelocale.do; CustomerHTMLAction.java; CustomerEJBAction.java</x:v>
+      </x:c>
+      <x:c r="I38" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="J38" s="65" t="str">
+        <x:v>Destination has no language/profile locale fields and no locale switcher.</x:v>
+      </x:c>
+      <x:c r="K38" s="65" t="str">
+        <x:v>AccountController.cs; account.component.ts; app.routes.ts</x:v>
+      </x:c>
+      <x:c r="L38" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M38" s="67" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="N38" s="65" t="str">
+        <x:v>specs/004-customer-accounts/plan.md DD-004 profile preferences deferred; specs/002-browse-product-catalog/plan.md localization out of scope</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A39" s="61" t="str"/>
+      <x:c r="B39" s="61" t="str"/>
+      <x:c r="C39" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D39" s="65" t="str">
+        <x:v>Customer can save a favorite category.</x:v>
+      </x:c>
+      <x:c r="E39" s="65" t="str">
+        <x:v>The legacy profile stores the customer's favorite pet category.</x:v>
+      </x:c>
+      <x:c r="F39" s="65" t="str">
+        <x:v>Favorite category is available for personalized shopping features.</x:v>
+      </x:c>
+      <x:c r="G39" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H39" s="65" t="str">
+        <x:v>create_customer.jsp; customer.jsp; edit_customer.jsp; ProfileEJB.java</x:v>
+      </x:c>
+      <x:c r="I39" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="J39" s="65" t="str">
+        <x:v>Destination account stores contact details only.</x:v>
+      </x:c>
+      <x:c r="K39" s="65" t="str">
+        <x:v>AccountController.cs; AccountDto.cs; account.component.ts</x:v>
+      </x:c>
+      <x:c r="L39" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M39" s="67" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="N39" s="65" t="str">
+        <x:v>specs/004-customer-accounts/plan.md DD-004 profile preferences deferred</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A40" s="61" t="str"/>
+      <x:c r="B40" s="61" t="str"/>
+      <x:c r="C40" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D40" s="65" t="str">
+        <x:v>MyList shows products from the favorite category when enabled.</x:v>
+      </x:c>
+      <x:c r="E40" s="65" t="str">
+        <x:v>The legacy experience can show a personalized product list based on the customer's favorite category.</x:v>
+      </x:c>
+      <x:c r="F40" s="65" t="str">
+        <x:v>Customer sees favorite-category products while shopping when the preference is enabled.</x:v>
+      </x:c>
+      <x:c r="G40" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H40" s="65" t="str">
+        <x:v>mylist.jsp; template.jsp; CustomerEJBAction.java</x:v>
+      </x:c>
+      <x:c r="I40" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="J40" s="65" t="str">
+        <x:v>Destination has no MyList feature or favorite-category personalization.</x:v>
+      </x:c>
+      <x:c r="K40" s="65" t="str">
+        <x:v>catalog-shell.component.ts; AccountController.cs</x:v>
+      </x:c>
+      <x:c r="L40" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M40" s="67" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="N40" s="65" t="str">
+        <x:v>specs/002-browse-product-catalog/spec.md personalized recommendations out of scope; specs/004-customer-accounts/plan.md DD-004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A41" s="61" t="str"/>
+      <x:c r="B41" s="61" t="str"/>
+      <x:c r="C41" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D41" s="65" t="str">
+        <x:v>Pet tips/advice banners are shown based on favorite category when enabled.</x:v>
+      </x:c>
+      <x:c r="E41" s="65" t="str">
+        <x:v>The legacy store can show advice banners personalized by customer profile.</x:v>
+      </x:c>
+      <x:c r="F41" s="65" t="str">
+        <x:v>Customer sees category-related advice while shopping when the preference is enabled.</x:v>
+      </x:c>
+      <x:c r="G41" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H41" s="65" t="str">
+        <x:v>advice_banner.jsp; BannerHelper.java; template.jsp</x:v>
+      </x:c>
+      <x:c r="I41" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="J41" s="65" t="str">
+        <x:v>Destination has no advice banner personalization.</x:v>
+      </x:c>
+      <x:c r="K41" s="65" t="str">
+        <x:v>catalog-shell.component.ts; AccountController.cs</x:v>
+      </x:c>
+      <x:c r="L41" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M41" s="67" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="N41" s="65" t="str">
+        <x:v>specs/002-browse-product-catalog/spec.md recommendation banners out of scope</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A42" s="61" t="str"/>
+      <x:c r="B42" s="61" t="str"/>
+      <x:c r="C42" s="61" t="str">
+        <x:v>Alternative path</x:v>
+      </x:c>
+      <x:c r="D42" s="65" t="str">
+        <x:v>Customer can enable or disable MyList and banner preferences.</x:v>
+      </x:c>
+      <x:c r="E42" s="65" t="str">
+        <x:v>Profile checkboxes control whether personalized list and advice features are used.</x:v>
+      </x:c>
+      <x:c r="F42" s="65" t="str">
+        <x:v>Customer preferences affect later shopping experience.</x:v>
+      </x:c>
+      <x:c r="G42" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H42" s="65" t="str">
+        <x:v>create_customer.jsp; edit_customer.jsp; CustomerHTMLAction.extractProfileInfo</x:v>
+      </x:c>
+      <x:c r="I42" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="J42" s="65" t="str">
+        <x:v>Destination has no profile preference toggles.</x:v>
+      </x:c>
+      <x:c r="K42" s="65" t="str">
+        <x:v>account.component.ts; RegisterRequestDto.cs</x:v>
+      </x:c>
+      <x:c r="L42" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M42" s="67" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="N42" s="65" t="str">
+        <x:v>specs/004-customer-accounts/plan.md DD-004 profile preferences deferred</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="37.5" customHeight="1" collapsed="1">
+      <x:c r="A43" s="67" t="str">
+        <x:v>UF-006</x:v>
+      </x:c>
+      <x:c r="B43" s="67" t="str">
+        <x:v>Shopping cart</x:v>
+      </x:c>
+      <x:c r="C43" s="67" t="str">
+        <x:v>Not Passed - Deferred/Partial</x:v>
+      </x:c>
+      <x:c r="D43" s="67" t="str">
+        <x:v>At least one requirement is partial, deferred, or a known gap.</x:v>
+      </x:c>
+      <x:c r="E43" s="67" t="str"/>
+      <x:c r="F43" s="67" t="str"/>
+      <x:c r="G43" s="67" t="str"/>
+      <x:c r="H43" s="67" t="str"/>
+      <x:c r="I43" s="67" t="str"/>
+      <x:c r="J43" s="67" t="str"/>
+      <x:c r="K43" s="67" t="str"/>
+      <x:c r="L43" s="67" t="str"/>
+      <x:c r="M43" s="67" t="str"/>
+      <x:c r="N43" s="67" t="str"/>
+    </x:row>
+    <x:row r="44" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A44" s="61" t="str"/>
+      <x:c r="B44" s="61" t="str"/>
+      <x:c r="C44" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D44" s="62" t="str">
+        <x:v>Visitor can add an item to the cart before signing in.</x:v>
+      </x:c>
+      <x:c r="E44" s="62" t="str">
+        <x:v>The cart is available during browsing and does not require authentication.</x:v>
+      </x:c>
+      <x:c r="F44" s="62" t="str">
+        <x:v>Item appears in the cart with quantity 1.</x:v>
+      </x:c>
+      <x:c r="G44" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H44" s="62" t="str">
+        <x:v>item.jsp; product.jsp; search.jsp; CartHTMLAction.java; CartEJBAction.java</x:v>
+      </x:c>
+      <x:c r="I44" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J44" s="62" t="str">
+        <x:v>Add-to-cart works anonymously using X-Cart-Id and also works after sign-in.</x:v>
+      </x:c>
+      <x:c r="K44" s="62" t="str">
+        <x:v>CartController.cs; CartIdentityResolver.cs; CartService.ts</x:v>
+      </x:c>
+      <x:c r="L44" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M44" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N44" s="62" t="str">
+        <x:v>specs/006-shopping-cart/spec.md FR-001, FR-007; specs/007-cart-ui/spec.md FR-001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A45" s="61" t="str"/>
+      <x:c r="B45" s="61" t="str"/>
+      <x:c r="C45" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D45" s="62" t="str">
+        <x:v>Adding the same item again increases quantity instead of creating duplicate lines.</x:v>
+      </x:c>
+      <x:c r="E45" s="62" t="str">
+        <x:v>A cart line represents an item with a quantity.</x:v>
+      </x:c>
+      <x:c r="F45" s="62" t="str">
+        <x:v>Cart shows one line with the increased quantity.</x:v>
+      </x:c>
+      <x:c r="G45" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H45" s="62" t="str">
+        <x:v>ShoppingCartLocalEJB.java; ShoppingCartModel.java; CartEJBAction.java</x:v>
+      </x:c>
+      <x:c r="I45" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J45" s="62" t="str">
+        <x:v>Backend add operation merges repeated item adds into the existing line.</x:v>
+      </x:c>
+      <x:c r="K45" s="62" t="str">
+        <x:v>CartRepository.cs; CartController.cs</x:v>
+      </x:c>
+      <x:c r="L45" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M45" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N45" s="62" t="str">
+        <x:v>specs/006-shopping-cart/spec.md FR-002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A46" s="61" t="str"/>
+      <x:c r="B46" s="61" t="str"/>
+      <x:c r="C46" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D46" s="62" t="str">
+        <x:v>Customer can view cart lines, quantities, prices, subtotals, and total.</x:v>
+      </x:c>
+      <x:c r="E46" s="62" t="str">
+        <x:v>The cart screen summarizes selected items and order value before checkout.</x:v>
+      </x:c>
+      <x:c r="F46" s="62" t="str">
+        <x:v>Cart shows lines and total cost.</x:v>
+      </x:c>
+      <x:c r="G46" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H46" s="62" t="str">
+        <x:v>cart.jsp; ShoppingCartModel.java; CartItem.java</x:v>
+      </x:c>
+      <x:c r="I46" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J46" s="62" t="str">
+        <x:v>Destination cart route and API return lines, subtotals, item count, total, and currency.</x:v>
+      </x:c>
+      <x:c r="K46" s="62" t="str">
+        <x:v>CartViewBuilder.cs; CartController.cs; cart.component.ts</x:v>
+      </x:c>
+      <x:c r="L46" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M46" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N46" s="62" t="str">
+        <x:v>specs/006-shopping-cart/spec.md FR-003; specs/007-cart-ui/spec.md FR-003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A47" s="61" t="str"/>
+      <x:c r="B47" s="61" t="str"/>
+      <x:c r="C47" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D47" s="62" t="str">
+        <x:v>Customer can update line quantities.</x:v>
+      </x:c>
+      <x:c r="E47" s="62" t="str">
+        <x:v>The cart update action accepts quantities for existing lines and recalculates totals.</x:v>
+      </x:c>
+      <x:c r="F47" s="62" t="str">
+        <x:v>Cart reflects changed quantities and totals.</x:v>
+      </x:c>
+      <x:c r="G47" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H47" s="62" t="str">
+        <x:v>cart.jsp; CartHTMLAction.java; CartEJBAction.java</x:v>
+      </x:c>
+      <x:c r="I47" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J47" s="62" t="str">
+        <x:v>Destination supports setting quantity per line and refreshes totals from backend.</x:v>
+      </x:c>
+      <x:c r="K47" s="62" t="str">
+        <x:v>CartController.cs; CartRepository.cs; cart.component.ts</x:v>
+      </x:c>
+      <x:c r="L47" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M47" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N47" s="62" t="str">
+        <x:v>specs/006-shopping-cart/spec.md FR-004; specs/007-cart-ui/spec.md FR-004, FR-005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A48" s="61" t="str"/>
+      <x:c r="B48" s="61" t="str"/>
+      <x:c r="C48" s="61" t="str">
+        <x:v>Alternative path</x:v>
+      </x:c>
+      <x:c r="D48" s="65" t="str">
+        <x:v>Invalid quantity input does not create a bad cart state.</x:v>
+      </x:c>
+      <x:c r="E48" s="65" t="str">
+        <x:v>Legacy non-numeric quantity input is coerced to zero; destination rejects negative/out-of-range input and treats zero as removal.</x:v>
+      </x:c>
+      <x:c r="F48" s="65" t="str">
+        <x:v>Cart remains usable and totals remain correct.</x:v>
+      </x:c>
+      <x:c r="G48" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H48" s="65" t="str">
+        <x:v>CartHTMLAction.java; CartEJBAction.java</x:v>
+      </x:c>
+      <x:c r="I48" s="65" t="str">
+        <x:v>Partially</x:v>
+      </x:c>
+      <x:c r="J48" s="65" t="str">
+        <x:v>Destination behavior is stricter than legacy: invalid or out-of-range quantities return validation errors; zero removes a line.</x:v>
+      </x:c>
+      <x:c r="K48" s="65" t="str">
+        <x:v>CartRules.cs; CartController.cs; cart.component.ts</x:v>
+      </x:c>
+      <x:c r="L48" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M48" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N48" s="65" t="str">
+        <x:v>specs/006-shopping-cart/spec.md FR-004 intentionally defines validation bounds</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A49" s="61" t="str"/>
+      <x:c r="B49" s="61" t="str"/>
+      <x:c r="C49" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D49" s="62" t="str">
+        <x:v>Customer can remove a cart line.</x:v>
+      </x:c>
+      <x:c r="E49" s="62" t="str">
+        <x:v>A customer can remove an item they no longer want.</x:v>
+      </x:c>
+      <x:c r="F49" s="62" t="str">
+        <x:v>The line disappears and totals update.</x:v>
+      </x:c>
+      <x:c r="G49" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H49" s="62" t="str">
+        <x:v>cart.jsp; CartHTMLAction.java; CartEJBAction.java</x:v>
+      </x:c>
+      <x:c r="I49" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J49" s="62" t="str">
+        <x:v>Destination supports removing a single cart line.</x:v>
+      </x:c>
+      <x:c r="K49" s="62" t="str">
+        <x:v>CartController.cs; cart.component.ts</x:v>
+      </x:c>
+      <x:c r="L49" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M49" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N49" s="62" t="str">
+        <x:v>specs/006-shopping-cart/spec.md FR-005; specs/007-cart-ui/spec.md FR-004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A50" s="61" t="str"/>
+      <x:c r="B50" s="61" t="str"/>
+      <x:c r="C50" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D50" s="65" t="str">
+        <x:v>Customer can empty the entire cart.</x:v>
+      </x:c>
+      <x:c r="E50" s="65" t="str">
+        <x:v>The cart feature should support clearing all selected items.</x:v>
+      </x:c>
+      <x:c r="F50" s="65" t="str">
+        <x:v>Cart returns to empty state.</x:v>
+      </x:c>
+      <x:c r="G50" s="65" t="str">
+        <x:v>Partially</x:v>
+      </x:c>
+      <x:c r="H50" s="65" t="str">
+        <x:v>CartHTMLAction.java comments mention emptying cart; cart.jsp exposes update/remove but no inspected empty action</x:v>
+      </x:c>
+      <x:c r="I50" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J50" s="65" t="str">
+        <x:v>Destination has an explicit empty-cart API and UI action.</x:v>
+      </x:c>
+      <x:c r="K50" s="65" t="str">
+        <x:v>CartController.cs; cart.component.ts</x:v>
+      </x:c>
+      <x:c r="L50" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M50" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N50" s="65" t="str">
+        <x:v>specs/006-shopping-cart/spec.md FR-005; specs/007-cart-ui/spec.md FR-004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A51" s="61" t="str"/>
+      <x:c r="B51" s="61" t="str"/>
+      <x:c r="C51" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D51" s="62" t="str">
+        <x:v>Cart survives navigation and sign-in transition.</x:v>
+      </x:c>
+      <x:c r="E51" s="62" t="str">
+        <x:v>The visitor's cart should remain available while browsing and merge into the customer cart after sign-in.</x:v>
+      </x:c>
+      <x:c r="F51" s="62" t="str">
+        <x:v>Selections are not lost when the customer signs in.</x:v>
+      </x:c>
+      <x:c r="G51" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H51" s="62" t="str">
+        <x:v>ShoppingCartLocalEJB.java; SignOnFilter.java</x:v>
+      </x:c>
+      <x:c r="I51" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J51" s="62" t="str">
+        <x:v>Destination persists anonymous cart id in localStorage and merges anonymous cart into user cart on authenticated requests.</x:v>
+      </x:c>
+      <x:c r="K51" s="62" t="str">
+        <x:v>CartIdentityResolver.cs; CartRepository.cs; CartService.ts</x:v>
+      </x:c>
+      <x:c r="L51" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M51" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N51" s="62" t="str">
+        <x:v>specs/006-shopping-cart/plan.md DD-001; specs/007-cart-ui/plan.md DD-001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="37.5" customHeight="1" collapsed="1">
+      <x:c r="A52" s="60" t="str">
+        <x:v>UF-007</x:v>
+      </x:c>
+      <x:c r="B52" s="60" t="str">
+        <x:v>Checkout and order placement</x:v>
+      </x:c>
+      <x:c r="C52" s="60" t="str">
+        <x:v>Not Passed - Missed</x:v>
+      </x:c>
+      <x:c r="D52" s="60" t="str">
+        <x:v>At least one source behavior is missing in destination and not covered/deferred in SDD.</x:v>
+      </x:c>
+      <x:c r="E52" s="60" t="str"/>
+      <x:c r="F52" s="60" t="str"/>
+      <x:c r="G52" s="60" t="str"/>
+      <x:c r="H52" s="60" t="str"/>
+      <x:c r="I52" s="60" t="str"/>
+      <x:c r="J52" s="60" t="str"/>
+      <x:c r="K52" s="60" t="str"/>
+      <x:c r="L52" s="60" t="str"/>
+      <x:c r="M52" s="60" t="str"/>
+      <x:c r="N52" s="60" t="str"/>
+    </x:row>
+    <x:row r="53" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A53" s="61" t="str"/>
+      <x:c r="B53" s="61" t="str"/>
+      <x:c r="C53" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D53" s="62" t="str">
+        <x:v>Checkout requires a signed-in customer.</x:v>
+      </x:c>
+      <x:c r="E53" s="62" t="str">
+        <x:v>A customer can browse and build a cart anonymously, but must authenticate before order placement.</x:v>
+      </x:c>
+      <x:c r="F53" s="62" t="str">
+        <x:v>Anonymous checkout redirects to sign-in; successful sign-in resumes checkout.</x:v>
+      </x:c>
+      <x:c r="G53" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H53" s="62" t="str">
+        <x:v>signon-config.xml; enter_order_information.screen</x:v>
+      </x:c>
+      <x:c r="I53" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J53" s="62" t="str">
+        <x:v>Checkout route is guarded by authGuard and backend order placement requires authorization.</x:v>
+      </x:c>
+      <x:c r="K53" s="62" t="str">
+        <x:v>app.routes.ts; auth.guard.ts; OrdersController.cs</x:v>
+      </x:c>
+      <x:c r="L53" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M53" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N53" s="62" t="str">
+        <x:v>specs/008-checkout-orders/spec.md FR-007; specs/005-account-ui/plan.md DD-003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A54" s="61" t="str"/>
+      <x:c r="B54" s="61" t="str"/>
+      <x:c r="C54" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D54" s="62" t="str">
+        <x:v>Checkout shows order review from the current cart.</x:v>
+      </x:c>
+      <x:c r="E54" s="62" t="str">
+        <x:v>Before placing an order, the customer can review selected items, quantities, and total.</x:v>
+      </x:c>
+      <x:c r="F54" s="62" t="str">
+        <x:v>Customer sees the cart lines and server-calculated total.</x:v>
+      </x:c>
+      <x:c r="G54" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H54" s="62" t="str">
+        <x:v>cart.jsp; enter_order_information.jsp; ShoppingCartModel.java</x:v>
+      </x:c>
+      <x:c r="I54" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J54" s="62" t="str">
+        <x:v>Destination checkout shows order review sourced from CartService/backend cart data.</x:v>
+      </x:c>
+      <x:c r="K54" s="62" t="str">
+        <x:v>checkout.component.ts; CartController.cs; CartViewBuilder.cs</x:v>
+      </x:c>
+      <x:c r="L54" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M54" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N54" s="62" t="str">
+        <x:v>specs/008-checkout-orders/spec.md FR-005; specs/007-cart-ui/spec.md FR-005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A55" s="61" t="str"/>
+      <x:c r="B55" s="61" t="str"/>
+      <x:c r="C55" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D55" s="62" t="str">
+        <x:v>Customer supplies billing and shipping contact information.</x:v>
+      </x:c>
+      <x:c r="E55" s="62" t="str">
+        <x:v>Legacy checkout captures separate billing and shipping contact blocks.</x:v>
+      </x:c>
+      <x:c r="F55" s="62" t="str">
+        <x:v>Order submission includes the contact information needed for fulfillment and confirmation.</x:v>
+      </x:c>
+      <x:c r="G55" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H55" s="62" t="str">
+        <x:v>enter_order_information.jsp; OrderHTMLAction.java</x:v>
+      </x:c>
+      <x:c r="I55" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J55" s="62" t="str">
+        <x:v>Destination checkout captures shipping contact and optional billing contact.</x:v>
+      </x:c>
+      <x:c r="K55" s="62" t="str">
+        <x:v>checkout.component.ts; OrdersController.cs; PlaceOrderRequestDto.cs</x:v>
+      </x:c>
+      <x:c r="L55" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M55" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N55" s="62" t="str">
+        <x:v>specs/008-checkout-orders/spec.md FR-001, FR-011</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A56" s="61" t="str"/>
+      <x:c r="B56" s="61" t="str"/>
+      <x:c r="C56" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D56" s="62" t="str">
+        <x:v>Checkout can prefill contact information from the customer account.</x:v>
+      </x:c>
+      <x:c r="E56" s="62" t="str">
+        <x:v>Legacy checkout fields use the signed-in customer's account contact values as defaults.</x:v>
+      </x:c>
+      <x:c r="F56" s="62" t="str">
+        <x:v>Customer does not need to retype known contact details.</x:v>
+      </x:c>
+      <x:c r="G56" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H56" s="62" t="str">
+        <x:v>enter_order_information.jsp; customer.account.contactInfo</x:v>
+      </x:c>
+      <x:c r="I56" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J56" s="62" t="str">
+        <x:v>Destination checkout pre-fills shipping contact from /api/account when available.</x:v>
+      </x:c>
+      <x:c r="K56" s="62" t="str">
+        <x:v>checkout.component.ts; AccountController.cs</x:v>
+      </x:c>
+      <x:c r="L56" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M56" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N56" s="62" t="str">
+        <x:v>specs/008-checkout-orders/spec.md FR-001; specs/005-account-ui/spec.md FR-005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A57" s="61" t="str"/>
+      <x:c r="B57" s="61" t="str"/>
+      <x:c r="C57" s="61" t="str">
+        <x:v>Legacy gap</x:v>
+      </x:c>
+      <x:c r="D57" s="65" t="str">
+        <x:v>Legacy checkout uses a hardcoded demo credit card.</x:v>
+      </x:c>
+      <x:c r="E57" s="65" t="str">
+        <x:v>The inspected legacy order action creates a fixed credit card value instead of collecting real card details at checkout.</x:v>
+      </x:c>
+      <x:c r="F57" s="65" t="str">
+        <x:v>Payment data behavior should be explicitly decided for migration.</x:v>
+      </x:c>
+      <x:c r="G57" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H57" s="65" t="str">
+        <x:v>OrderHTMLAction.java</x:v>
+      </x:c>
+      <x:c r="I57" s="65" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="J57" s="65" t="str">
+        <x:v>Destination intentionally captures no card data and stores no payment card information.</x:v>
+      </x:c>
+      <x:c r="K57" s="65" t="str">
+        <x:v>PlaceOrderRequestDto.cs; OrdersController.cs</x:v>
+      </x:c>
+      <x:c r="L57" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M57" s="67" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="N57" s="65" t="str">
+        <x:v>specs/008-checkout-orders/spec.md DP-003 resolved: no card data captured or stored; specs/004-customer-accounts/plan.md DD-003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A58" s="61" t="str"/>
+      <x:c r="B58" s="61" t="str"/>
+      <x:c r="C58" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D58" s="62" t="str">
+        <x:v>Successful checkout creates a unique order id with status pending.</x:v>
+      </x:c>
+      <x:c r="E58" s="62" t="str">
+        <x:v>The system turns the cart into a purchase order with a generated id and starts order processing.</x:v>
+      </x:c>
+      <x:c r="F58" s="62" t="str">
+        <x:v>Customer sees an order id and pending order state.</x:v>
+      </x:c>
+      <x:c r="G58" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H58" s="62" t="str">
+        <x:v>OrderEJBAction.java; UniqueIdGeneratorEJB.java; order_completed.jsp</x:v>
+      </x:c>
+      <x:c r="I58" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J58" s="62" t="str">
+        <x:v>Destination creates a persisted order, returns the generated id, and starts with PENDING status.</x:v>
+      </x:c>
+      <x:c r="K58" s="62" t="str">
+        <x:v>OrdersController.cs; OrderPlacementService.cs; OrderStatus.cs; checkout.component.ts</x:v>
+      </x:c>
+      <x:c r="L58" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M58" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N58" s="62" t="str">
+        <x:v>specs/008-checkout-orders/spec.md FR-002, FR-003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A59" s="61" t="str"/>
+      <x:c r="B59" s="61" t="str"/>
+      <x:c r="C59" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D59" s="62" t="str">
+        <x:v>Successful checkout empties the cart.</x:v>
+      </x:c>
+      <x:c r="E59" s="62" t="str">
+        <x:v>After the order is placed, selected items should no longer remain in the active cart.</x:v>
+      </x:c>
+      <x:c r="F59" s="62" t="str">
+        <x:v>Cart is empty after successful order placement.</x:v>
+      </x:c>
+      <x:c r="G59" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H59" s="62" t="str">
+        <x:v>OrderEJBAction.java</x:v>
+      </x:c>
+      <x:c r="I59" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J59" s="62" t="str">
+        <x:v>Destination placement runs cart emptying in the placement transaction and refreshes the cart.</x:v>
+      </x:c>
+      <x:c r="K59" s="62" t="str">
+        <x:v>OrderPlacementService.cs; checkout.component.ts</x:v>
+      </x:c>
+      <x:c r="L59" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M59" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N59" s="62" t="str">
+        <x:v>specs/008-checkout-orders/spec.md FR-006; specs/008-checkout-orders/plan.md DD-002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A60" s="61" t="str"/>
+      <x:c r="B60" s="61" t="str"/>
+      <x:c r="C60" s="61" t="str">
+        <x:v>Alternative path</x:v>
+      </x:c>
+      <x:c r="D60" s="62" t="str">
+        <x:v>Empty cart cannot be ordered.</x:v>
+      </x:c>
+      <x:c r="E60" s="62" t="str">
+        <x:v>If the cart has no items, the order should not be created.</x:v>
+      </x:c>
+      <x:c r="F60" s="62" t="str">
+        <x:v>Customer sees an empty-cart order error and no order is placed.</x:v>
+      </x:c>
+      <x:c r="G60" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H60" s="62" t="str">
+        <x:v>OrderEJBAction.java; cart_empty_order_error.jsp; mappings.xml</x:v>
+      </x:c>
+      <x:c r="I60" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J60" s="62" t="str">
+        <x:v>Destination rejects empty-cart placement and creates nothing.</x:v>
+      </x:c>
+      <x:c r="K60" s="62" t="str">
+        <x:v>OrderPlacementRules.cs; OrderPlacementService.cs; OrdersController.cs; checkout.component.ts</x:v>
+      </x:c>
+      <x:c r="L60" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M60" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N60" s="62" t="str">
+        <x:v>specs/008-checkout-orders/spec.md FR-007; specs/008-checkout-orders/plan.md DD-002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A61" s="61" t="str"/>
+      <x:c r="B61" s="61" t="str"/>
+      <x:c r="C61" s="61" t="str">
+        <x:v>Alternative path</x:v>
+      </x:c>
+      <x:c r="D61" s="62" t="str">
+        <x:v>Missing checkout contact fields are rejected.</x:v>
+      </x:c>
+      <x:c r="E61" s="62" t="str">
+        <x:v>Required checkout contact information must be present before an order can be created.</x:v>
+      </x:c>
+      <x:c r="F61" s="62" t="str">
+        <x:v>Customer gets validation feedback and no invalid order is created.</x:v>
+      </x:c>
+      <x:c r="G61" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H61" s="62" t="str">
+        <x:v>OrderHTMLAction.java; MissingFormDataException.java</x:v>
+      </x:c>
+      <x:c r="I61" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J61" s="62" t="str">
+        <x:v>Destination validates shipping and optional billing contact fields.</x:v>
+      </x:c>
+      <x:c r="K61" s="62" t="str">
+        <x:v>OrdersController.cs; ContactValidation.cs; checkout.component.ts</x:v>
+      </x:c>
+      <x:c r="L61" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M61" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N61" s="62" t="str">
+        <x:v>specs/008-checkout-orders/spec.md FR-007; specs/008-checkout-orders/spec.md SC-006</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A62" s="61" t="str"/>
+      <x:c r="B62" s="61" t="str"/>
+      <x:c r="C62" s="61" t="str">
+        <x:v>Gap</x:v>
+      </x:c>
+      <x:c r="D62" s="64" t="str">
+        <x:v>Customer is told to expect a confirmation email after order placement.</x:v>
+      </x:c>
+      <x:c r="E62" s="64" t="str">
+        <x:v>The legacy confirmation page promises a confirmation email to the billing email address.</x:v>
+      </x:c>
+      <x:c r="F62" s="64" t="str">
+        <x:v>Customer expects a confirmation email after order completion.</x:v>
+      </x:c>
+      <x:c r="G62" s="64" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H62" s="64" t="str">
+        <x:v>order_completed.jsp; OrderEventResponse.java</x:v>
+      </x:c>
+      <x:c r="I62" s="64" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="J62" s="64" t="str">
+        <x:v>No migrated mail confirmation feature or email-sending path exists for order placement.</x:v>
+      </x:c>
+      <x:c r="K62" s="64" t="str">
+        <x:v>OrdersController.cs; OrderPlacementService.cs; Mailer-related destination code not present</x:v>
+      </x:c>
+      <x:c r="L62" s="64" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="M62" s="64" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N62" s="64" t="str">
+        <x:v>No matching SDD requirement or explicit deferral found in specs/008-checkout-orders, specs/010-order-processing, or specs/011-supplier-fulfillment.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="37.5" customHeight="1" collapsed="1">
+      <x:c r="A63" s="67" t="str">
+        <x:v>UF-008</x:v>
+      </x:c>
+      <x:c r="B63" s="67" t="str">
+        <x:v>Order lifecycle after placement</x:v>
+      </x:c>
+      <x:c r="C63" s="67" t="str">
+        <x:v>Not Passed - Deferred/Partial</x:v>
+      </x:c>
+      <x:c r="D63" s="67" t="str">
+        <x:v>At least one requirement is partial, deferred, or a known gap.</x:v>
+      </x:c>
+      <x:c r="E63" s="67" t="str"/>
+      <x:c r="F63" s="67" t="str"/>
+      <x:c r="G63" s="67" t="str"/>
+      <x:c r="H63" s="67" t="str"/>
+      <x:c r="I63" s="67" t="str"/>
+      <x:c r="J63" s="67" t="str"/>
+      <x:c r="K63" s="67" t="str"/>
+      <x:c r="L63" s="67" t="str"/>
+      <x:c r="M63" s="67" t="str"/>
+      <x:c r="N63" s="67" t="str"/>
+    </x:row>
+    <x:row r="64" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A64" s="61" t="str"/>
+      <x:c r="B64" s="61" t="str"/>
+      <x:c r="C64" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D64" s="62" t="str">
+        <x:v>Placed orders enter backend processing after checkout.</x:v>
+      </x:c>
+      <x:c r="E64" s="62" t="str">
+        <x:v>Legacy checkout submits purchase order data asynchronously for operational processing.</x:v>
+      </x:c>
+      <x:c r="F64" s="62" t="str">
+        <x:v>Order can later be approved, denied, shipped, or completed.</x:v>
+      </x:c>
+      <x:c r="G64" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H64" s="62" t="str">
+        <x:v>OrderEJBAction.java; AsyncSenderEJB.java; purchaseorder component</x:v>
+      </x:c>
+      <x:c r="I64" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J64" s="62" t="str">
+        <x:v>Destination persists orders and evaluates eligible new orders through order-processing services.</x:v>
+      </x:c>
+      <x:c r="K64" s="62" t="str">
+        <x:v>OrderPlacementService.cs; OrderProcessingService.cs; OrderStatus.cs</x:v>
+      </x:c>
+      <x:c r="L64" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M64" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N64" s="62" t="str">
+        <x:v>specs/008-checkout-orders/spec.md FR-011, FR-012; specs/010-order-processing/spec.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A65" s="61" t="str"/>
+      <x:c r="B65" s="61" t="str"/>
+      <x:c r="C65" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D65" s="62" t="str">
+        <x:v>Order lines freeze item id, category, product, quantity, and unit price at placement time.</x:v>
+      </x:c>
+      <x:c r="E65" s="62" t="str">
+        <x:v>The order record should not depend on mutable cart state after placement.</x:v>
+      </x:c>
+      <x:c r="F65" s="62" t="str">
+        <x:v>Later processing and admin views see the purchased lines as placed.</x:v>
+      </x:c>
+      <x:c r="G65" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H65" s="62" t="str">
+        <x:v>OrderEJBAction.java; LineItem.java; PurchaseOrder.java</x:v>
+      </x:c>
+      <x:c r="I65" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J65" s="62" t="str">
+        <x:v>Destination freezes item id, name, unit price, currency, quantity, and category-related data for analytics.</x:v>
+      </x:c>
+      <x:c r="K65" s="62" t="str">
+        <x:v>OrderPlacementService.cs; OrderLineEntity.cs; AdminSalesAnalyticsRepository.cs</x:v>
+      </x:c>
+      <x:c r="L65" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M65" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N65" s="62" t="str">
+        <x:v>specs/008-checkout-orders/spec.md FR-004, FR-011; specs/015-admin-sales-analytics/spec.md FR-002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A66" s="61" t="str"/>
+      <x:c r="B66" s="61" t="str"/>
+      <x:c r="C66" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D66" s="62" t="str">
+        <x:v>Small or eligible pending orders can be auto-approved.</x:v>
+      </x:c>
+      <x:c r="E66" s="62" t="str">
+        <x:v>Operational processing may move an order from pending to approved without manual admin action when it meets the configured rule.</x:v>
+      </x:c>
+      <x:c r="F66" s="62" t="str">
+        <x:v>Eligible orders continue toward fulfillment automatically.</x:v>
+      </x:c>
+      <x:c r="G66" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H66" s="62" t="str">
+        <x:v>OPC/admin/order processing components; processmanager components</x:v>
+      </x:c>
+      <x:c r="I66" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J66" s="62" t="str">
+        <x:v>Destination auto-approves orders below the configured threshold and immediately attempts fulfillment.</x:v>
+      </x:c>
+      <x:c r="K66" s="62" t="str">
+        <x:v>OrderProcessingService.cs; appsettings.json; OrderTransitionRepository.cs</x:v>
+      </x:c>
+      <x:c r="L66" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M66" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N66" s="62" t="str">
+        <x:v>specs/010-order-processing/spec.md; OrderProcessingServiceTests.cs</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A67" s="61" t="str"/>
+      <x:c r="B67" s="61" t="str"/>
+      <x:c r="C67" s="61" t="str">
+        <x:v>Alternative path</x:v>
+      </x:c>
+      <x:c r="D67" s="62" t="str">
+        <x:v>Orders can remain pending for administrator decision.</x:v>
+      </x:c>
+      <x:c r="E67" s="62" t="str">
+        <x:v>Orders that are not auto-approved wait for an admin approval or denial.</x:v>
+      </x:c>
+      <x:c r="F67" s="62" t="str">
+        <x:v>Admin sees pending orders and can decide them.</x:v>
+      </x:c>
+      <x:c r="G67" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H67" s="62" t="str">
+        <x:v>AdminRequestProcessor.java; ApplRequestProcessor.java; OrdersApprovePanel.java</x:v>
+      </x:c>
+      <x:c r="I67" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J67" s="62" t="str">
+        <x:v>Destination keeps pending orders available to admin order endpoints and UI.</x:v>
+      </x:c>
+      <x:c r="K67" s="62" t="str">
+        <x:v>AdminOrdersController.cs; pending-orders.component.ts</x:v>
+      </x:c>
+      <x:c r="L67" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M67" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N67" s="62" t="str">
+        <x:v>specs/010-order-processing/spec.md; specs/012-admin-ui/spec.md FR-002, FR-003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A68" s="61" t="str"/>
+      <x:c r="B68" s="61" t="str"/>
+      <x:c r="C68" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D68" s="62" t="str">
+        <x:v>Approved orders attempt supplier fulfillment.</x:v>
+      </x:c>
+      <x:c r="E68" s="62" t="str">
+        <x:v>Once approved, an order should be matched against inventory and shipped where possible.</x:v>
+      </x:c>
+      <x:c r="F68" s="62" t="str">
+        <x:v>Order status moves toward shipped/completed or partially shipped.</x:v>
+      </x:c>
+      <x:c r="G68" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H68" s="62" t="str">
+        <x:v>supplier orderfulfillment components; SupplierOrderMDB.java; OrderFulfillmentFacadeEJB.java</x:v>
+      </x:c>
+      <x:c r="I68" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J68" s="62" t="str">
+        <x:v>Destination fulfillment ships available quantities and records shipment evidence.</x:v>
+      </x:c>
+      <x:c r="K68" s="62" t="str">
+        <x:v>FulfillmentService.cs; InventoryRepository.cs; ShipmentEntity.cs</x:v>
+      </x:c>
+      <x:c r="L68" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M68" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N68" s="62" t="str">
+        <x:v>specs/011-supplier-fulfillment/spec.md; specs/013-supplier-role-access/spec.md FR-007</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A69" s="61" t="str"/>
+      <x:c r="B69" s="61" t="str"/>
+      <x:c r="C69" s="61" t="str">
+        <x:v>Alternative path</x:v>
+      </x:c>
+      <x:c r="D69" s="62" t="str">
+        <x:v>Insufficient inventory can create partial shipment/backorder behavior.</x:v>
+      </x:c>
+      <x:c r="E69" s="62" t="str">
+        <x:v>If stock is not enough for all ordered quantities, the system should preserve what shipped and allow later completion.</x:v>
+      </x:c>
+      <x:c r="F69" s="62" t="str">
+        <x:v>Order can wait in a partially shipped state until inventory is replenished.</x:v>
+      </x:c>
+      <x:c r="G69" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H69" s="62" t="str">
+        <x:v>Supplier fulfillment components; SupplierOrder.java; OrderStatusNames.java</x:v>
+      </x:c>
+      <x:c r="I69" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J69" s="62" t="str">
+        <x:v>Destination uses SHIPPED_PART and fulfills remaining lines after inventory replenishment.</x:v>
+      </x:c>
+      <x:c r="K69" s="62" t="str">
+        <x:v>FulfillmentService.cs; FulfillmentRules.cs; SupplierInventoryController.cs</x:v>
+      </x:c>
+      <x:c r="L69" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M69" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N69" s="62" t="str">
+        <x:v>specs/011-supplier-fulfillment/spec.md; specs/013-supplier-role-access/spec.md SC-004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A70" s="61" t="str"/>
+      <x:c r="B70" s="61" t="str"/>
+      <x:c r="C70" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D70" s="65" t="str">
+        <x:v>Completed fulfillment can produce invoice/shipment evidence.</x:v>
+      </x:c>
+      <x:c r="E70" s="65" t="str">
+        <x:v>Legacy supplier processing sends invoice documents after processing pending purchase orders.</x:v>
+      </x:c>
+      <x:c r="F70" s="65" t="str">
+        <x:v>Operational processing has evidence that items were shipped.</x:v>
+      </x:c>
+      <x:c r="G70" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H70" s="65" t="str">
+        <x:v>RcvrRequestProcessor.java; TPASupplierOrderXDE.java; TPAInvoiceXDE.java</x:v>
+      </x:c>
+      <x:c r="I70" s="65" t="str">
+        <x:v>Partially</x:v>
+      </x:c>
+      <x:c r="J70" s="65" t="str">
+        <x:v>Destination records shipments and shipment lines, but does not produce/send legacy XML invoice documents.</x:v>
+      </x:c>
+      <x:c r="K70" s="65" t="str">
+        <x:v>FulfillmentService.cs; ShipmentEntity.cs; ShipmentLineEntity.cs</x:v>
+      </x:c>
+      <x:c r="L70" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M70" s="67" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="N70" s="65" t="str">
+        <x:v>specs/011-supplier-fulfillment/spec.md preserves fulfillment behavior; legacy XML invoice transport is not preserved in first slice</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="37.5" customHeight="1" collapsed="1">
+      <x:c r="A71" s="67" t="str">
+        <x:v>UF-009</x:v>
+      </x:c>
+      <x:c r="B71" s="67" t="str">
+        <x:v>Customer account view and update</x:v>
+      </x:c>
+      <x:c r="C71" s="67" t="str">
+        <x:v>Not Passed - Deferred/Partial</x:v>
+      </x:c>
+      <x:c r="D71" s="67" t="str">
+        <x:v>At least one requirement is partial, deferred, or a known gap.</x:v>
+      </x:c>
+      <x:c r="E71" s="67" t="str"/>
+      <x:c r="F71" s="67" t="str"/>
+      <x:c r="G71" s="67" t="str"/>
+      <x:c r="H71" s="67" t="str"/>
+      <x:c r="I71" s="67" t="str"/>
+      <x:c r="J71" s="67" t="str"/>
+      <x:c r="K71" s="67" t="str"/>
+      <x:c r="L71" s="67" t="str"/>
+      <x:c r="M71" s="67" t="str"/>
+      <x:c r="N71" s="67" t="str"/>
+    </x:row>
+    <x:row r="72" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A72" s="61" t="str"/>
+      <x:c r="B72" s="61" t="str"/>
+      <x:c r="C72" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D72" s="65" t="str">
+        <x:v>Signed-in customer can view their account contact, payment, profile, and preferences.</x:v>
+      </x:c>
+      <x:c r="E72" s="65" t="str">
+        <x:v>The legacy customer screen displays stored account/contact, card, language, favorite category, MyList, and banner preferences.</x:v>
+      </x:c>
+      <x:c r="F72" s="65" t="str">
+        <x:v>Customer can review the account information the store has saved.</x:v>
+      </x:c>
+      <x:c r="G72" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H72" s="65" t="str">
+        <x:v>customer.jsp; CustomerEJBAction.java; customer component</x:v>
+      </x:c>
+      <x:c r="I72" s="65" t="str">
+        <x:v>Partially</x:v>
+      </x:c>
+      <x:c r="J72" s="65" t="str">
+        <x:v>Destination account view reads and displays contact information only.</x:v>
+      </x:c>
+      <x:c r="K72" s="65" t="str">
+        <x:v>AccountController.cs; account.component.ts; AccountDto.cs</x:v>
+      </x:c>
+      <x:c r="L72" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M72" s="67" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="N72" s="65" t="str">
+        <x:v>specs/005-account-ui/spec.md FR-005; specs/004-customer-accounts/plan.md DD-003, DD-004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A73" s="61" t="str"/>
+      <x:c r="B73" s="61" t="str"/>
+      <x:c r="C73" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D73" s="62" t="str">
+        <x:v>Signed-in customer can update contact details.</x:v>
+      </x:c>
+      <x:c r="E73" s="62" t="str">
+        <x:v>A customer can change the account contact information used later by checkout.</x:v>
+      </x:c>
+      <x:c r="F73" s="62" t="str">
+        <x:v>Saved contact details are updated and visible afterward.</x:v>
+      </x:c>
+      <x:c r="G73" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H73" s="62" t="str">
+        <x:v>edit_customer.jsp; CustomerHTMLAction.java; CustomerEJBAction.java</x:v>
+      </x:c>
+      <x:c r="I73" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J73" s="62" t="str">
+        <x:v>Destination lets signed-in customers update contact details with validation.</x:v>
+      </x:c>
+      <x:c r="K73" s="62" t="str">
+        <x:v>AccountController.cs; account.component.ts; ContactValidation.cs</x:v>
+      </x:c>
+      <x:c r="L73" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M73" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N73" s="62" t="str">
+        <x:v>specs/004-customer-accounts/spec.md FR-006; specs/005-account-ui/spec.md FR-005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A74" s="61" t="str"/>
+      <x:c r="B74" s="61" t="str"/>
+      <x:c r="C74" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D74" s="65" t="str">
+        <x:v>Signed-in customer can update credit card information.</x:v>
+      </x:c>
+      <x:c r="E74" s="65" t="str">
+        <x:v>Legacy account update stores card number, card type, and expiry as part of the account.</x:v>
+      </x:c>
+      <x:c r="F74" s="65" t="str">
+        <x:v>Saved payment information changes with the account.</x:v>
+      </x:c>
+      <x:c r="G74" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H74" s="65" t="str">
+        <x:v>edit_customer.jsp; CustomerHTMLAction.extractCreditCard; CustomerEJBAction.java</x:v>
+      </x:c>
+      <x:c r="I74" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="J74" s="65" t="str">
+        <x:v>Destination intentionally stores no credit card data.</x:v>
+      </x:c>
+      <x:c r="K74" s="65" t="str">
+        <x:v>AccountController.cs; CustomerContactEntity.cs</x:v>
+      </x:c>
+      <x:c r="L74" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M74" s="67" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="N74" s="65" t="str">
+        <x:v>specs/004-customer-accounts/plan.md DD-003 no credit card storage</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A75" s="61" t="str"/>
+      <x:c r="B75" s="61" t="str"/>
+      <x:c r="C75" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D75" s="65" t="str">
+        <x:v>Signed-in customer can update profile preferences.</x:v>
+      </x:c>
+      <x:c r="E75" s="65" t="str">
+        <x:v>Legacy account update stores preferred language, favorite category, MyList, and banner preferences.</x:v>
+      </x:c>
+      <x:c r="F75" s="65" t="str">
+        <x:v>Personalized shopping preferences change after saving.</x:v>
+      </x:c>
+      <x:c r="G75" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H75" s="65" t="str">
+        <x:v>edit_customer.jsp; CustomerHTMLAction.extractProfileInfo; CustomerEJBAction.java</x:v>
+      </x:c>
+      <x:c r="I75" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="J75" s="65" t="str">
+        <x:v>Destination has no profile preference fields or preference update API.</x:v>
+      </x:c>
+      <x:c r="K75" s="65" t="str">
+        <x:v>AccountController.cs; account.component.ts</x:v>
+      </x:c>
+      <x:c r="L75" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M75" s="67" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="N75" s="65" t="str">
+        <x:v>specs/004-customer-accounts/plan.md DD-004 profile preferences deferred</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A76" s="61" t="str"/>
+      <x:c r="B76" s="61" t="str"/>
+      <x:c r="C76" s="61" t="str">
+        <x:v>Alternative path</x:v>
+      </x:c>
+      <x:c r="D76" s="62" t="str">
+        <x:v>Missing required account contact fields are rejected.</x:v>
+      </x:c>
+      <x:c r="E76" s="62" t="str">
+        <x:v>Required account contact details must be present before saving.</x:v>
+      </x:c>
+      <x:c r="F76" s="62" t="str">
+        <x:v>Customer receives validation feedback and invalid contact data is not saved.</x:v>
+      </x:c>
+      <x:c r="G76" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H76" s="62" t="str">
+        <x:v>CustomerHTMLAction.java; MissingFormDataException.java</x:v>
+      </x:c>
+      <x:c r="I76" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J76" s="62" t="str">
+        <x:v>Destination validates required contact fields and returns a clear error.</x:v>
+      </x:c>
+      <x:c r="K76" s="62" t="str">
+        <x:v>AccountController.cs; ContactValidation.cs; account.component.ts</x:v>
+      </x:c>
+      <x:c r="L76" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M76" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N76" s="62" t="str">
+        <x:v>specs/004-customer-accounts/spec.md FR-006; specs/005-account-ui/spec.md FR-008</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="37.5" customHeight="1" collapsed="1">
+      <x:c r="A77" s="69" t="str">
+        <x:v>UF-010</x:v>
+      </x:c>
+      <x:c r="B77" s="69" t="str">
+        <x:v>User sign-out</x:v>
+      </x:c>
+      <x:c r="C77" s="69" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="D77" s="69" t="str">
+        <x:v>All requirements are covered in source, destination, and SDD.</x:v>
+      </x:c>
+      <x:c r="E77" s="69" t="str"/>
+      <x:c r="F77" s="69" t="str"/>
+      <x:c r="G77" s="69" t="str"/>
+      <x:c r="H77" s="69" t="str"/>
+      <x:c r="I77" s="69" t="str"/>
+      <x:c r="J77" s="69" t="str"/>
+      <x:c r="K77" s="69" t="str"/>
+      <x:c r="L77" s="69" t="str"/>
+      <x:c r="M77" s="69" t="str"/>
+      <x:c r="N77" s="69" t="str"/>
+    </x:row>
+    <x:row r="78" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A78" s="61" t="str"/>
+      <x:c r="B78" s="61" t="str"/>
+      <x:c r="C78" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D78" s="62" t="str">
+        <x:v>Signed-in customer can sign out.</x:v>
+      </x:c>
+      <x:c r="E78" s="62" t="str">
+        <x:v>The customer can end the signed-in state from the store experience.</x:v>
+      </x:c>
+      <x:c r="F78" s="62" t="str">
+        <x:v>The store shows the customer as signed out.</x:v>
+      </x:c>
+      <x:c r="G78" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H78" s="62" t="str">
+        <x:v>banner.jsp; signoff.do; SignOffHTMLAction.java; signoff.jsp</x:v>
+      </x:c>
+      <x:c r="I78" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J78" s="62" t="str">
+        <x:v>Destination sign-out clears client identity and token; shell returns to anonymous state.</x:v>
+      </x:c>
+      <x:c r="K78" s="62" t="str">
+        <x:v>identity.service.ts; catalog-shell.component.ts</x:v>
+      </x:c>
+      <x:c r="L78" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M78" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N78" s="62" t="str">
+        <x:v>specs/004-customer-accounts/spec.md FR-004; specs/005-account-ui/spec.md FR-003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A79" s="61" t="str"/>
+      <x:c r="B79" s="61" t="str"/>
+      <x:c r="C79" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D79" s="62" t="str">
+        <x:v>After sign-out, protected customer functionality requires sign-in again.</x:v>
+      </x:c>
+      <x:c r="E79" s="62" t="str">
+        <x:v>Account, checkout, and order actions should no longer be available as the previous user.</x:v>
+      </x:c>
+      <x:c r="F79" s="62" t="str">
+        <x:v>Protected actions redirect or reject until the user signs in again.</x:v>
+      </x:c>
+      <x:c r="G79" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H79" s="62" t="str">
+        <x:v>SignOnFilter.java; signon-config.xml</x:v>
+      </x:c>
+      <x:c r="I79" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J79" s="62" t="str">
+        <x:v>Cleared JWT identity removes authorization; guards and backend authorization reject protected calls.</x:v>
+      </x:c>
+      <x:c r="K79" s="62" t="str">
+        <x:v>identity.service.ts; auth.guard.ts; auth.interceptor.ts; OrdersController.cs</x:v>
+      </x:c>
+      <x:c r="L79" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M79" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N79" s="62" t="str">
+        <x:v>specs/004-customer-accounts/plan.md DD-001; specs/005-account-ui/spec.md FR-006</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A80" s="61" t="str"/>
+      <x:c r="B80" s="61" t="str"/>
+      <x:c r="C80" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D80" s="62" t="str">
+        <x:v>Sign-out page gives the customer a way to sign in again.</x:v>
+      </x:c>
+      <x:c r="E80" s="62" t="str">
+        <x:v>The legacy sign-off confirmation offers a sign-in link.</x:v>
+      </x:c>
+      <x:c r="F80" s="62" t="str">
+        <x:v>Customer can start sign-in again from the signed-out state.</x:v>
+      </x:c>
+      <x:c r="G80" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H80" s="62" t="str">
+        <x:v>signoff.jsp</x:v>
+      </x:c>
+      <x:c r="I80" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J80" s="62" t="str">
+        <x:v>Destination shell immediately shows the sign-in link after sign-out.</x:v>
+      </x:c>
+      <x:c r="K80" s="62" t="str">
+        <x:v>catalog-shell.component.ts; identity.service.ts</x:v>
+      </x:c>
+      <x:c r="L80" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M80" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N80" s="62" t="str">
+        <x:v>specs/005-account-ui/spec.md FR-002, FR-003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="37.5" customHeight="1" collapsed="1">
+      <x:c r="A81" s="67" t="str">
+        <x:v>UF-011</x:v>
+      </x:c>
+      <x:c r="B81" s="67" t="str">
+        <x:v>Admin access and launch</x:v>
+      </x:c>
+      <x:c r="C81" s="67" t="str">
+        <x:v>Not Passed - Deferred/Partial</x:v>
+      </x:c>
+      <x:c r="D81" s="67" t="str">
+        <x:v>At least one requirement is partial, deferred, or a known gap.</x:v>
+      </x:c>
+      <x:c r="E81" s="67" t="str"/>
+      <x:c r="F81" s="67" t="str"/>
+      <x:c r="G81" s="67" t="str"/>
+      <x:c r="H81" s="67" t="str"/>
+      <x:c r="I81" s="67" t="str"/>
+      <x:c r="J81" s="67" t="str"/>
+      <x:c r="K81" s="67" t="str"/>
+      <x:c r="L81" s="67" t="str"/>
+      <x:c r="M81" s="67" t="str"/>
+      <x:c r="N81" s="67" t="str"/>
+    </x:row>
+    <x:row r="82" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A82" s="61" t="str"/>
+      <x:c r="B82" s="61" t="str"/>
+      <x:c r="C82" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D82" s="62" t="str">
+        <x:v>Administrator must authenticate before opening admin operations.</x:v>
+      </x:c>
+      <x:c r="E82" s="62" t="str">
+        <x:v>The legacy admin web module protects its admin processor with an administrator role.</x:v>
+      </x:c>
+      <x:c r="F82" s="62" t="str">
+        <x:v>Unauthenticated/non-admin users cannot access admin tools.</x:v>
+      </x:c>
+      <x:c r="G82" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H82" s="62" t="str">
+        <x:v>src/apps/admin/src/docroot/WEB-INF/web.xml; login.jsp; error.jsp</x:v>
+      </x:c>
+      <x:c r="I82" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J82" s="62" t="str">
+        <x:v>Destination admin routes and APIs require admin role.</x:v>
+      </x:c>
+      <x:c r="K82" s="62" t="str">
+        <x:v>admin.guard.ts; AdminOrdersController.cs; AdminSalesAnalyticsController.cs; app.routes.ts</x:v>
+      </x:c>
+      <x:c r="L82" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M82" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N82" s="62" t="str">
+        <x:v>specs/012-admin-ui/spec.md FR-001, FR-009; specs/013-supplier-role-access/spec.md FR-003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A83" s="61" t="str"/>
+      <x:c r="B83" s="61" t="str"/>
+      <x:c r="C83" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D83" s="62" t="str">
+        <x:v>Administrator can launch the order-management experience.</x:v>
+      </x:c>
+      <x:c r="E83" s="62" t="str">
+        <x:v>Legacy admin web starts a Java Web Start rich client for order management.</x:v>
+      </x:c>
+      <x:c r="F83" s="62" t="str">
+        <x:v>Administrator reaches the admin order tools after login.</x:v>
+      </x:c>
+      <x:c r="G83" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H83" s="62" t="str">
+        <x:v>AdminRequestProcessor.java; index.jsp; PetStoreAdminClient.java</x:v>
+      </x:c>
+      <x:c r="I83" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J83" s="62" t="str">
+        <x:v>Destination replaces JNLP/rich client launch with an Angular admin route area.</x:v>
+      </x:c>
+      <x:c r="K83" s="62" t="str">
+        <x:v>AdminShellComponent.ts; app.routes.ts; admin-api.service.ts</x:v>
+      </x:c>
+      <x:c r="L83" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M83" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N83" s="62" t="str">
+        <x:v>specs/012-admin-ui/spec.md FR-009; specs/012-admin-ui/spec.md DP-001 resolved as admin route area</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A84" s="61" t="str"/>
+      <x:c r="B84" s="61" t="str"/>
+      <x:c r="C84" s="61" t="str">
+        <x:v>Alternative path</x:v>
+      </x:c>
+      <x:c r="D84" s="62" t="str">
+        <x:v>Invalid admin credentials show a login error.</x:v>
+      </x:c>
+      <x:c r="E84" s="62" t="str">
+        <x:v>If admin authentication fails, the admin app shows an error instead of launching tools.</x:v>
+      </x:c>
+      <x:c r="F84" s="62" t="str">
+        <x:v>User remains outside admin tools.</x:v>
+      </x:c>
+      <x:c r="G84" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H84" s="62" t="str">
+        <x:v>src/apps/admin/src/docroot/login.jsp; error.jsp; web.xml</x:v>
+      </x:c>
+      <x:c r="I84" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J84" s="62" t="str">
+        <x:v>Destination sign-in returns invalid credentials and admin guard blocks non-admin identities.</x:v>
+      </x:c>
+      <x:c r="K84" s="62" t="str">
+        <x:v>AuthController.cs; sign-in.component.ts; admin.guard.ts</x:v>
+      </x:c>
+      <x:c r="L84" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M84" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N84" s="62" t="str">
+        <x:v>specs/004-customer-accounts/spec.md FR-008; specs/012-admin-ui/spec.md FR-001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A85" s="61" t="str"/>
+      <x:c r="B85" s="61" t="str"/>
+      <x:c r="C85" s="61" t="str">
+        <x:v>Alternative path</x:v>
+      </x:c>
+      <x:c r="D85" s="65" t="str">
+        <x:v>Admin session timeout produces an error for rich-client calls.</x:v>
+      </x:c>
+      <x:c r="E85" s="65" t="str">
+        <x:v>Legacy rich-client requests fail with a session-timeout message when the server session is gone.</x:v>
+      </x:c>
+      <x:c r="F85" s="65" t="str">
+        <x:v>Admin is told to exit and log in again.</x:v>
+      </x:c>
+      <x:c r="G85" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H85" s="65" t="str">
+        <x:v>ApplRequestProcessor.java</x:v>
+      </x:c>
+      <x:c r="I85" s="65" t="str">
+        <x:v>Partially</x:v>
+      </x:c>
+      <x:c r="J85" s="65" t="str">
+        <x:v>Destination relies on JWT expiry/401 handling; the exact legacy session-timeout message is not preserved.</x:v>
+      </x:c>
+      <x:c r="K85" s="65" t="str">
+        <x:v>auth.interceptor.ts; admin.guard.ts</x:v>
+      </x:c>
+      <x:c r="L85" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M85" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N85" s="65" t="str">
+        <x:v>specs/005-account-ui/plan.md DD-002; specs/012-admin-ui/spec.md FR-008</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="37.5" customHeight="1" collapsed="1">
+      <x:c r="A86" s="69" t="str">
+        <x:v>UF-012</x:v>
+      </x:c>
+      <x:c r="B86" s="69" t="str">
+        <x:v>Admin order management</x:v>
+      </x:c>
+      <x:c r="C86" s="69" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="D86" s="69" t="str">
+        <x:v>All requirements are covered in source, destination, and SDD.</x:v>
+      </x:c>
+      <x:c r="E86" s="69" t="str"/>
+      <x:c r="F86" s="69" t="str"/>
+      <x:c r="G86" s="69" t="str"/>
+      <x:c r="H86" s="69" t="str"/>
+      <x:c r="I86" s="69" t="str"/>
+      <x:c r="J86" s="69" t="str"/>
+      <x:c r="K86" s="69" t="str"/>
+      <x:c r="L86" s="69" t="str"/>
+      <x:c r="M86" s="69" t="str"/>
+      <x:c r="N86" s="69" t="str"/>
+    </x:row>
+    <x:row r="87" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A87" s="61" t="str"/>
+      <x:c r="B87" s="61" t="str"/>
+      <x:c r="C87" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D87" s="62" t="str">
+        <x:v>Administrator can list pending orders.</x:v>
+      </x:c>
+      <x:c r="E87" s="62" t="str">
+        <x:v>Admin order tools fetch orders by status so pending orders can be reviewed.</x:v>
+      </x:c>
+      <x:c r="F87" s="62" t="str">
+        <x:v>Pending orders show id, customer, date, amount, and status.</x:v>
+      </x:c>
+      <x:c r="G87" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H87" s="62" t="str">
+        <x:v>ApplRequestProcessor.java GETORDERS; AdminRequestBD.java; OrdersApprovePanel.java</x:v>
+      </x:c>
+      <x:c r="I87" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J87" s="62" t="str">
+        <x:v>Destination pending-orders view lists PENDING orders with core details.</x:v>
+      </x:c>
+      <x:c r="K87" s="62" t="str">
+        <x:v>AdminOrdersController.cs; pending-orders.component.ts</x:v>
+      </x:c>
+      <x:c r="L87" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M87" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N87" s="62" t="str">
+        <x:v>specs/012-admin-ui/spec.md FR-002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A88" s="61" t="str"/>
+      <x:c r="B88" s="61" t="str"/>
+      <x:c r="C88" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D88" s="62" t="str">
+        <x:v>Administrator can approve a pending order.</x:v>
+      </x:c>
+      <x:c r="E88" s="62" t="str">
+        <x:v>Admin approval changes a pending order so fulfillment can continue.</x:v>
+      </x:c>
+      <x:c r="F88" s="62" t="str">
+        <x:v>Order leaves the pending queue and moves to approved/fulfillment processing.</x:v>
+      </x:c>
+      <x:c r="G88" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H88" s="62" t="str">
+        <x:v>ApplRequestProcessor.java UPDATESTATUS; OrderApproval.java; OrdersApprovePanel.java</x:v>
+      </x:c>
+      <x:c r="I88" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J88" s="62" t="str">
+        <x:v>Destination approve endpoint transitions pending orders and triggers fulfillment.</x:v>
+      </x:c>
+      <x:c r="K88" s="62" t="str">
+        <x:v>AdminOrdersController.cs; OrderProcessingService.cs; pending-orders.component.ts</x:v>
+      </x:c>
+      <x:c r="L88" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M88" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N88" s="62" t="str">
+        <x:v>specs/010-order-processing/spec.md; specs/012-admin-ui/spec.md FR-003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A89" s="61" t="str"/>
+      <x:c r="B89" s="61" t="str"/>
+      <x:c r="C89" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D89" s="62" t="str">
+        <x:v>Administrator can deny a pending order.</x:v>
+      </x:c>
+      <x:c r="E89" s="62" t="str">
+        <x:v>Admin denial stops a pending order from continuing through fulfillment.</x:v>
+      </x:c>
+      <x:c r="F89" s="62" t="str">
+        <x:v>Order leaves the pending queue with denied status.</x:v>
+      </x:c>
+      <x:c r="G89" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H89" s="62" t="str">
+        <x:v>ApplRequestProcessor.java UPDATESTATUS; OrderApproval.java; OrdersApprovePanel.java</x:v>
+      </x:c>
+      <x:c r="I89" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J89" s="62" t="str">
+        <x:v>Destination deny endpoint transitions pending orders to DENIED.</x:v>
+      </x:c>
+      <x:c r="K89" s="62" t="str">
+        <x:v>AdminOrdersController.cs; OrderProcessingService.cs; pending-orders.component.ts</x:v>
+      </x:c>
+      <x:c r="L89" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M89" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N89" s="62" t="str">
+        <x:v>specs/010-order-processing/spec.md; specs/012-admin-ui/spec.md FR-003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A90" s="61" t="str"/>
+      <x:c r="B90" s="61" t="str"/>
+      <x:c r="C90" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D90" s="62" t="str">
+        <x:v>Administrator can apply one decision to multiple selected pending orders.</x:v>
+      </x:c>
+      <x:c r="E90" s="62" t="str">
+        <x:v>Legacy admin client supports table-based order selection and submitting status updates for multiple orders.</x:v>
+      </x:c>
+      <x:c r="F90" s="62" t="str">
+        <x:v>Each selected order receives approval/denial feedback.</x:v>
+      </x:c>
+      <x:c r="G90" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H90" s="62" t="str">
+        <x:v>OrdersApprovePanel.java; DataSource.java; ApplRequestProcessor.updateOrders</x:v>
+      </x:c>
+      <x:c r="I90" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J90" s="62" t="str">
+        <x:v>Destination pending UI supports selected orders and sequential per-order decision calls with per-order outcome.</x:v>
+      </x:c>
+      <x:c r="K90" s="62" t="str">
+        <x:v>pending-orders.component.ts; AdminApiService.ts</x:v>
+      </x:c>
+      <x:c r="L90" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M90" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N90" s="62" t="str">
+        <x:v>specs/012-admin-ui/spec.md FR-003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A91" s="61" t="str"/>
+      <x:c r="B91" s="61" t="str"/>
+      <x:c r="C91" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D91" s="62" t="str">
+        <x:v>Administrator can browse orders by status.</x:v>
+      </x:c>
+      <x:c r="E91" s="62" t="str">
+        <x:v>Admin tools can retrieve orders beyond the pending queue by requested status.</x:v>
+      </x:c>
+      <x:c r="F91" s="62" t="str">
+        <x:v>Orders matching the chosen status are listed.</x:v>
+      </x:c>
+      <x:c r="G91" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H91" s="62" t="str">
+        <x:v>ApplRequestProcessor.getOrders; AdminRequestBD.getOrdersByStatus; OrdersViewPanel.java</x:v>
+      </x:c>
+      <x:c r="I91" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J91" s="62" t="str">
+        <x:v>Destination all-orders admin view filters by all canonical statuses.</x:v>
+      </x:c>
+      <x:c r="K91" s="62" t="str">
+        <x:v>AdminOrdersController.cs; admin-order-list.component.ts; admin.models.ts</x:v>
+      </x:c>
+      <x:c r="L91" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M91" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N91" s="62" t="str">
+        <x:v>specs/012-admin-ui/spec.md FR-004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A92" s="61" t="str"/>
+      <x:c r="B92" s="61" t="str"/>
+      <x:c r="C92" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D92" s="62" t="str">
+        <x:v>Administrator can view order details.</x:v>
+      </x:c>
+      <x:c r="E92" s="62" t="str">
+        <x:v>Admin tools provide enough order detail to inspect lines, customer contact, totals, and status.</x:v>
+      </x:c>
+      <x:c r="F92" s="62" t="str">
+        <x:v>Admin can understand a specific order before or after decisions.</x:v>
+      </x:c>
+      <x:c r="G92" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H92" s="62" t="str">
+        <x:v>OrderDetails.java; DataSource.java; OrdersViewPanel.java</x:v>
+      </x:c>
+      <x:c r="I92" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J92" s="62" t="str">
+        <x:v>Destination admin order detail shows lines, totals, contact info, status, and transition history.</x:v>
+      </x:c>
+      <x:c r="K92" s="62" t="str">
+        <x:v>AdminOrdersController.cs; admin-order-detail.component.ts</x:v>
+      </x:c>
+      <x:c r="L92" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M92" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N92" s="62" t="str">
+        <x:v>specs/012-admin-ui/spec.md FR-005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A93" s="61" t="str"/>
+      <x:c r="B93" s="61" t="str"/>
+      <x:c r="C93" s="61" t="str">
+        <x:v>Alternative path</x:v>
+      </x:c>
+      <x:c r="D93" s="62" t="str">
+        <x:v>Invalid or stale admin order decisions are rejected.</x:v>
+      </x:c>
+      <x:c r="E93" s="62" t="str">
+        <x:v>If an order is already decided or not pending, another decision should not silently corrupt status.</x:v>
+      </x:c>
+      <x:c r="F93" s="62" t="str">
+        <x:v>Admin sees the decision failed or was already decided.</x:v>
+      </x:c>
+      <x:c r="G93" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H93" s="62" t="str">
+        <x:v>ApplRequestProcessor.updateOrders; processmanager transitions</x:v>
+      </x:c>
+      <x:c r="I93" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J93" s="62" t="str">
+        <x:v>Destination returns conflict for invalid transitions; UI shows Already decided feedback.</x:v>
+      </x:c>
+      <x:c r="K93" s="62" t="str">
+        <x:v>AdminOrdersController.cs; OrderTransitionRepository.cs; pending-orders.component.ts</x:v>
+      </x:c>
+      <x:c r="L93" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M93" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N93" s="62" t="str">
+        <x:v>specs/012-admin-ui/spec.md edge cases; specs/010-order-processing/spec.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="37.5" customHeight="1" collapsed="1">
+      <x:c r="A94" s="67" t="str">
+        <x:v>UF-013</x:v>
+      </x:c>
+      <x:c r="B94" s="67" t="str">
+        <x:v>Admin sales analytics</x:v>
+      </x:c>
+      <x:c r="C94" s="67" t="str">
+        <x:v>Not Passed - Deferred/Partial</x:v>
+      </x:c>
+      <x:c r="D94" s="67" t="str">
+        <x:v>At least one requirement is partial, deferred, or a known gap.</x:v>
+      </x:c>
+      <x:c r="E94" s="67" t="str"/>
+      <x:c r="F94" s="67" t="str"/>
+      <x:c r="G94" s="67" t="str"/>
+      <x:c r="H94" s="67" t="str"/>
+      <x:c r="I94" s="67" t="str"/>
+      <x:c r="J94" s="67" t="str"/>
+      <x:c r="K94" s="67" t="str"/>
+      <x:c r="L94" s="67" t="str"/>
+      <x:c r="M94" s="67" t="str"/>
+      <x:c r="N94" s="67" t="str"/>
+    </x:row>
+    <x:row r="95" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A95" s="61" t="str"/>
+      <x:c r="B95" s="61" t="str"/>
+      <x:c r="C95" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D95" s="62" t="str">
+        <x:v>Administrator can view revenue share by category for a date range.</x:v>
+      </x:c>
+      <x:c r="E95" s="62" t="str">
+        <x:v>Legacy admin pie chart shows total sales revenue split by category over selected dates.</x:v>
+      </x:c>
+      <x:c r="F95" s="62" t="str">
+        <x:v>Admin sees category revenue amounts and percentages.</x:v>
+      </x:c>
+      <x:c r="G95" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H95" s="62" t="str">
+        <x:v>PieChartPanel.java; DataSource.java; ApplRequestProcessor.java request=REVENUE</x:v>
+      </x:c>
+      <x:c r="I95" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J95" s="62" t="str">
+        <x:v>Destination admin sales dashboard consumes sales analytics with revenue amount and percentage per category.</x:v>
+      </x:c>
+      <x:c r="K95" s="62" t="str">
+        <x:v>AdminSalesAnalyticsController.cs; AdminSalesAnalyticsService.cs; sales-dashboard.component.ts</x:v>
+      </x:c>
+      <x:c r="L95" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M95" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N95" s="62" t="str">
+        <x:v>specs/015-admin-sales-analytics/spec.md FR-001, FR-002, FR-003, FR-007; specs/016-admin-sales-charts-ui/spec.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A96" s="61" t="str"/>
+      <x:c r="B96" s="61" t="str"/>
+      <x:c r="C96" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D96" s="62" t="str">
+        <x:v>Administrator can view sales count by category for a date range.</x:v>
+      </x:c>
+      <x:c r="E96" s="62" t="str">
+        <x:v>Legacy admin bar chart shows total number of sold items/orders by category over selected dates.</x:v>
+      </x:c>
+      <x:c r="F96" s="62" t="str">
+        <x:v>Admin sees category sales-count bars.</x:v>
+      </x:c>
+      <x:c r="G96" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H96" s="62" t="str">
+        <x:v>BarChartPanel.java; DataSource.java; ApplRequestProcessor.java request=ORDERS</x:v>
+      </x:c>
+      <x:c r="I96" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J96" s="62" t="str">
+        <x:v>Destination response includes sales count per category and UI renders a bar chart.</x:v>
+      </x:c>
+      <x:c r="K96" s="62" t="str">
+        <x:v>AdminSalesAnalyticsController.cs; AdminSalesAnalyticsService.cs; sales-dashboard.component.ts</x:v>
+      </x:c>
+      <x:c r="L96" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M96" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N96" s="62" t="str">
+        <x:v>specs/015-admin-sales-analytics/spec.md FR-004, FR-007; specs/016-admin-sales-charts-ui/plan.md DD-004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A97" s="61" t="str"/>
+      <x:c r="B97" s="61" t="str"/>
+      <x:c r="C97" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D97" s="62" t="str">
+        <x:v>Administrator can change chart date range.</x:v>
+      </x:c>
+      <x:c r="E97" s="62" t="str">
+        <x:v>Legacy chart panels accept start and end dates and submit them to refresh chart data.</x:v>
+      </x:c>
+      <x:c r="F97" s="62" t="str">
+        <x:v>Charts reflect only orders inside the requested range.</x:v>
+      </x:c>
+      <x:c r="G97" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H97" s="62" t="str">
+        <x:v>PieChartPanel.java; BarChartPanel.java; ApplRequestProcessor.getProperDate</x:v>
+      </x:c>
+      <x:c r="I97" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J97" s="62" t="str">
+        <x:v>Destination dashboard has date inputs and backend filters by placement date.</x:v>
+      </x:c>
+      <x:c r="K97" s="62" t="str">
+        <x:v>SalesAnalyticsDateRangeRequest.cs; AdminSalesAnalyticsRepository.cs; sales-dashboard.component.ts</x:v>
+      </x:c>
+      <x:c r="L97" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M97" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N97" s="62" t="str">
+        <x:v>specs/015-admin-sales-analytics/spec.md FR-005, FR-010; specs/015-admin-sales-analytics/plan.md DD-003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A98" s="61" t="str"/>
+      <x:c r="B98" s="61" t="str"/>
+      <x:c r="C98" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D98" s="62" t="str">
+        <x:v>Sales analytics are admin-only.</x:v>
+      </x:c>
+      <x:c r="E98" s="62" t="str">
+        <x:v>Sales information is business-sensitive and belongs to the admin capability boundary.</x:v>
+      </x:c>
+      <x:c r="F98" s="62" t="str">
+        <x:v>Non-admin users cannot view sales analytics.</x:v>
+      </x:c>
+      <x:c r="G98" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H98" s="62" t="str">
+        <x:v>src/apps/admin/src/docroot/WEB-INF/web.xml; ApplRequestProcessor.java</x:v>
+      </x:c>
+      <x:c r="I98" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J98" s="62" t="str">
+        <x:v>Destination protects the sales analytics API and route with admin authorization.</x:v>
+      </x:c>
+      <x:c r="K98" s="62" t="str">
+        <x:v>AdminSalesAnalyticsController.cs; admin.guard.ts; app.routes.ts</x:v>
+      </x:c>
+      <x:c r="L98" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M98" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N98" s="62" t="str">
+        <x:v>specs/015-admin-sales-analytics/spec.md FR-009; specs/016-admin-sales-charts-ui/plan.md constraints</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A99" s="61" t="str"/>
+      <x:c r="B99" s="61" t="str"/>
+      <x:c r="C99" s="61" t="str">
+        <x:v>Alternative path</x:v>
+      </x:c>
+      <x:c r="D99" s="65" t="str">
+        <x:v>Invalid chart date input is rejected clearly.</x:v>
+      </x:c>
+      <x:c r="E99" s="65" t="str">
+        <x:v>The system should not produce misleading chart data for invalid date ranges.</x:v>
+      </x:c>
+      <x:c r="F99" s="65" t="str">
+        <x:v>Admin receives a validation error instead of bad chart data.</x:v>
+      </x:c>
+      <x:c r="G99" s="65" t="str">
+        <x:v>Partially</x:v>
+      </x:c>
+      <x:c r="H99" s="65" t="str">
+        <x:v>ApplRequestProcessor.getProperDate; PieChartPanel.java; BarChartPanel.java</x:v>
+      </x:c>
+      <x:c r="I99" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J99" s="65" t="str">
+        <x:v>Destination validates date format/range and returns ApiErrorDto; UI shows unavailable/error states.</x:v>
+      </x:c>
+      <x:c r="K99" s="65" t="str">
+        <x:v>SalesAnalyticsDateRangeRequest.cs; AdminSalesAnalyticsController.cs; sales-dashboard.component.ts</x:v>
+      </x:c>
+      <x:c r="L99" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M99" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N99" s="65" t="str">
+        <x:v>specs/015-admin-sales-analytics/spec.md FR-010; specs/016-admin-sales-charts-ui/spec.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A100" s="61" t="str"/>
+      <x:c r="B100" s="61" t="str"/>
+      <x:c r="C100" s="61" t="str">
+        <x:v>Deferred</x:v>
+      </x:c>
+      <x:c r="D100" s="65" t="str">
+        <x:v>Legacy chart protocol can request item-level detail for a selected category.</x:v>
+      </x:c>
+      <x:c r="E100" s="65" t="str">
+        <x:v>When a category is supplied, legacy chart responses switch from Category elements to Item elements.</x:v>
+      </x:c>
+      <x:c r="F100" s="65" t="str">
+        <x:v>Admin could inspect sales within a category at item level.</x:v>
+      </x:c>
+      <x:c r="G100" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H100" s="65" t="str">
+        <x:v>ApplRequestProcessor.getChartInfo; PieChartPanel.java</x:v>
+      </x:c>
+      <x:c r="I100" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="J100" s="65" t="str">
+        <x:v>Destination first implementation supports category-level analytics only.</x:v>
+      </x:c>
+      <x:c r="K100" s="65" t="str">
+        <x:v>AdminSalesAnalyticsService.cs; AdminSalesAnalyticsRepository.cs; sales-dashboard.component.ts</x:v>
+      </x:c>
+      <x:c r="L100" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M100" s="67" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="N100" s="65" t="str">
+        <x:v>specs/015-admin-sales-analytics/spec.md out of scope: item-level drilldown; specs/015-admin-sales-analytics/plan.md scale/scope</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="37.5" customHeight="1" collapsed="1">
+      <x:c r="A101" s="67" t="str">
+        <x:v>UF-014</x:v>
+      </x:c>
+      <x:c r="B101" s="67" t="str">
+        <x:v>Supplier access</x:v>
+      </x:c>
+      <x:c r="C101" s="67" t="str">
+        <x:v>Not Passed - Deferred/Partial</x:v>
+      </x:c>
+      <x:c r="D101" s="67" t="str">
+        <x:v>At least one requirement is partial, deferred, or a known gap.</x:v>
+      </x:c>
+      <x:c r="E101" s="67" t="str"/>
+      <x:c r="F101" s="67" t="str"/>
+      <x:c r="G101" s="67" t="str"/>
+      <x:c r="H101" s="67" t="str"/>
+      <x:c r="I101" s="67" t="str"/>
+      <x:c r="J101" s="67" t="str"/>
+      <x:c r="K101" s="67" t="str"/>
+      <x:c r="L101" s="67" t="str"/>
+      <x:c r="M101" s="67" t="str"/>
+      <x:c r="N101" s="67" t="str"/>
+    </x:row>
+    <x:row r="102" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A102" s="61" t="str"/>
+      <x:c r="B102" s="61" t="str"/>
+      <x:c r="C102" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D102" s="62" t="str">
+        <x:v>Supplier operator must authenticate before inventory operations.</x:v>
+      </x:c>
+      <x:c r="E102" s="62" t="str">
+        <x:v>The legacy supplier web module protects inventory processing with an administrator role in its own app boundary.</x:v>
+      </x:c>
+      <x:c r="F102" s="62" t="str">
+        <x:v>Unauthenticated users cannot operate supplier inventory.</x:v>
+      </x:c>
+      <x:c r="G102" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H102" s="62" t="str">
+        <x:v>src/apps/supplier/src/docroot/WEB-INF/web.xml; login.jsp; error.jsp</x:v>
+      </x:c>
+      <x:c r="I102" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J102" s="62" t="str">
+        <x:v>Destination has supplier role/policy and guarded supplier route.</x:v>
+      </x:c>
+      <x:c r="K102" s="62" t="str">
+        <x:v>SupplierInventoryController.cs; supplier.guard.ts; Program.cs</x:v>
+      </x:c>
+      <x:c r="L102" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M102" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N102" s="62" t="str">
+        <x:v>specs/013-supplier-role-access/spec.md FR-001, FR-004; specs/014-supplier-ui-access/spec.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A103" s="61" t="str"/>
+      <x:c r="B103" s="61" t="str"/>
+      <x:c r="C103" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D103" s="62" t="str">
+        <x:v>Supplier identity is separate from ordinary customer identity.</x:v>
+      </x:c>
+      <x:c r="E103" s="62" t="str">
+        <x:v>Legacy supplier used a distinct application/principal boundary for inventory operations.</x:v>
+      </x:c>
+      <x:c r="F103" s="62" t="str">
+        <x:v>Customer identity cannot perform supplier operations.</x:v>
+      </x:c>
+      <x:c r="G103" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H103" s="62" t="str">
+        <x:v>src/apps/supplier/src/docroot/WEB-INF/web.xml; supplier app context</x:v>
+      </x:c>
+      <x:c r="I103" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J103" s="62" t="str">
+        <x:v>Destination seeds supplier role and rejects customer/anonymous callers for inventory and fulfillment.</x:v>
+      </x:c>
+      <x:c r="K103" s="62" t="str">
+        <x:v>UserEntity.cs; SupplierInventoryController.cs; SupplierRoleApiContractTests.cs</x:v>
+      </x:c>
+      <x:c r="L103" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M103" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N103" s="62" t="str">
+        <x:v>specs/013-supplier-role-access/spec.md FR-001, FR-002, FR-004, FR-005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A104" s="61" t="str"/>
+      <x:c r="B104" s="61" t="str"/>
+      <x:c r="C104" s="61" t="str">
+        <x:v>Alternative path</x:v>
+      </x:c>
+      <x:c r="D104" s="65" t="str">
+        <x:v>Supplier can log out or leave the supplier experience.</x:v>
+      </x:c>
+      <x:c r="E104" s="65" t="str">
+        <x:v>Legacy supplier offers logout from the supplier inventory pages.</x:v>
+      </x:c>
+      <x:c r="F104" s="65" t="str">
+        <x:v>Supplier session can end and access requires authentication again.</x:v>
+      </x:c>
+      <x:c r="G104" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H104" s="65" t="str">
+        <x:v>index.jsp; back.jsp; logout.jsp; RcvrRequestProcessor.java</x:v>
+      </x:c>
+      <x:c r="I104" s="65" t="str">
+        <x:v>Partially</x:v>
+      </x:c>
+      <x:c r="J104" s="65" t="str">
+        <x:v>Destination supplier uses the shared sign-out behavior from identity shell, not a separate supplier logout page.</x:v>
+      </x:c>
+      <x:c r="K104" s="65" t="str">
+        <x:v>identity.service.ts; catalog-shell.component.ts; supplier.guard.ts</x:v>
+      </x:c>
+      <x:c r="L104" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M104" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N104" s="65" t="str">
+        <x:v>specs/005-account-ui/spec.md FR-003; specs/014-supplier-ui-access/spec.md route access</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="37.5" customHeight="1" collapsed="1">
+      <x:c r="A105" s="67" t="str">
+        <x:v>UF-015</x:v>
+      </x:c>
+      <x:c r="B105" s="67" t="str">
+        <x:v>Supplier inventory and fulfillment</x:v>
+      </x:c>
+      <x:c r="C105" s="67" t="str">
+        <x:v>Not Passed - Deferred/Partial</x:v>
+      </x:c>
+      <x:c r="D105" s="67" t="str">
+        <x:v>At least one requirement is partial, deferred, or a known gap.</x:v>
+      </x:c>
+      <x:c r="E105" s="67" t="str"/>
+      <x:c r="F105" s="67" t="str"/>
+      <x:c r="G105" s="67" t="str"/>
+      <x:c r="H105" s="67" t="str"/>
+      <x:c r="I105" s="67" t="str"/>
+      <x:c r="J105" s="67" t="str"/>
+      <x:c r="K105" s="67" t="str"/>
+      <x:c r="L105" s="67" t="str"/>
+      <x:c r="M105" s="67" t="str"/>
+      <x:c r="N105" s="67" t="str"/>
+    </x:row>
+    <x:row r="106" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A106" s="61" t="str"/>
+      <x:c r="B106" s="61" t="str"/>
+      <x:c r="C106" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D106" s="62" t="str">
+        <x:v>Supplier can view current inventory for all items.</x:v>
+      </x:c>
+      <x:c r="E106" s="62" t="str">
+        <x:v>The supplier inventory page lists item ids and existing quantities.</x:v>
+      </x:c>
+      <x:c r="F106" s="62" t="str">
+        <x:v>Supplier sees stock levels before editing.</x:v>
+      </x:c>
+      <x:c r="G106" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H106" s="62" t="str">
+        <x:v>displayinventory.jsp; DisplayInventoryBean.java; InventoryEJB.java</x:v>
+      </x:c>
+      <x:c r="I106" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J106" s="62" t="str">
+        <x:v>Destination supplier inventory view lists item ids and on-hand quantities.</x:v>
+      </x:c>
+      <x:c r="K106" s="62" t="str">
+        <x:v>SupplierInventoryController.cs; InventoryRepository.cs; inventory.component.ts</x:v>
+      </x:c>
+      <x:c r="L106" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M106" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N106" s="62" t="str">
+        <x:v>specs/013-supplier-role-access/spec.md FR-004; specs/012-admin-ui/spec.md FR-006</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A107" s="61" t="str"/>
+      <x:c r="B107" s="61" t="str"/>
+      <x:c r="C107" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D107" s="62" t="str">
+        <x:v>Supplier can set a new non-negative quantity for selected items.</x:v>
+      </x:c>
+      <x:c r="E107" s="62" t="str">
+        <x:v>The legacy supplier page asks for new quantities and only updates checked items with non-negative values.</x:v>
+      </x:c>
+      <x:c r="F107" s="62" t="str">
+        <x:v>Saved inventory reflects the new quantity.</x:v>
+      </x:c>
+      <x:c r="G107" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H107" s="62" t="str">
+        <x:v>displayinventory.jsp; RcvrRequestProcessor.updateInventory</x:v>
+      </x:c>
+      <x:c r="I107" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J107" s="62" t="str">
+        <x:v>Destination validates non-negative quantity and persists confirmed values.</x:v>
+      </x:c>
+      <x:c r="K107" s="62" t="str">
+        <x:v>SupplierInventoryController.cs; InventoryRepository.cs; inventory.component.ts</x:v>
+      </x:c>
+      <x:c r="L107" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M107" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N107" s="62" t="str">
+        <x:v>specs/013-supplier-role-access/spec.md FR-004, FR-007</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A108" s="61" t="str"/>
+      <x:c r="B108" s="61" t="str"/>
+      <x:c r="C108" s="61" t="str">
+        <x:v>Alternative path</x:v>
+      </x:c>
+      <x:c r="D108" s="65" t="str">
+        <x:v>Blank inventory quantity input is ignored.</x:v>
+      </x:c>
+      <x:c r="E108" s="65" t="str">
+        <x:v>Legacy supplier update skips empty new-quantity fields instead of failing the whole update.</x:v>
+      </x:c>
+      <x:c r="F108" s="65" t="str">
+        <x:v>Only supplied item quantities change.</x:v>
+      </x:c>
+      <x:c r="G108" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H108" s="65" t="str">
+        <x:v>RcvrRequestProcessor.updateInventory</x:v>
+      </x:c>
+      <x:c r="I108" s="65" t="str">
+        <x:v>Partially</x:v>
+      </x:c>
+      <x:c r="J108" s="65" t="str">
+        <x:v>Destination updates one item at a time and requires a concrete quantity for that request.</x:v>
+      </x:c>
+      <x:c r="K108" s="65" t="str">
+        <x:v>SupplierInventoryController.cs; inventory.component.ts</x:v>
+      </x:c>
+      <x:c r="L108" s="65" t="str">
+        <x:v>Partially</x:v>
+      </x:c>
+      <x:c r="M108" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N108" s="65" t="str">
+        <x:v>specs/013-supplier-role-access/spec.md FR-004 covers non-negative update, but not blank-field batch behavior.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A109" s="61" t="str"/>
+      <x:c r="B109" s="61" t="str"/>
+      <x:c r="C109" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D109" s="62" t="str">
+        <x:v>Successful inventory update triggers processing of pending supplier orders.</x:v>
+      </x:c>
+      <x:c r="E109" s="62" t="str">
+        <x:v>After supplier inventory changes, legacy processing checks pending purchase orders and sends invoices.</x:v>
+      </x:c>
+      <x:c r="F109" s="62" t="str">
+        <x:v>Backordered orders can continue after stock is replenished.</x:v>
+      </x:c>
+      <x:c r="G109" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H109" s="62" t="str">
+        <x:v>RcvrRequestProcessor.java; OrderFulfillmentFacadeEJB.java; SupplierOrderTD.java</x:v>
+      </x:c>
+      <x:c r="I109" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J109" s="62" t="str">
+        <x:v>Destination inventory update automatically re-runs fulfillment for affected orders.</x:v>
+      </x:c>
+      <x:c r="K109" s="62" t="str">
+        <x:v>SupplierInventoryController.cs; FulfillmentService.cs</x:v>
+      </x:c>
+      <x:c r="L109" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M109" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N109" s="62" t="str">
+        <x:v>specs/013-supplier-role-access/spec.md DP-002, FR-007; specs/013-supplier-role-access/plan.md DD-002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A110" s="61" t="str"/>
+      <x:c r="B110" s="61" t="str"/>
+      <x:c r="C110" s="61" t="str">
+        <x:v>Happy path</x:v>
+      </x:c>
+      <x:c r="D110" s="62" t="str">
+        <x:v>Supplier receives success feedback after inventory update.</x:v>
+      </x:c>
+      <x:c r="E110" s="62" t="str">
+        <x:v>Legacy supplier forwards to a confirmation page after update and processing.</x:v>
+      </x:c>
+      <x:c r="F110" s="62" t="str">
+        <x:v>Supplier sees that inventory was updated successfully.</x:v>
+      </x:c>
+      <x:c r="G110" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="H110" s="62" t="str">
+        <x:v>back.jsp; RcvrRequestProcessor.java</x:v>
+      </x:c>
+      <x:c r="I110" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J110" s="62" t="str">
+        <x:v>Destination reloads inventory after save and shows confirmed current quantities/errors.</x:v>
+      </x:c>
+      <x:c r="K110" s="62" t="str">
+        <x:v>inventory.component.ts; SupplierInventoryController.cs</x:v>
+      </x:c>
+      <x:c r="L110" s="62" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M110" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N110" s="62" t="str">
+        <x:v>specs/014-supplier-ui-access/spec.md; specs/012-admin-ui/spec.md FR-008</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="66" customHeight="1" outlineLevel="1" hidden="1">
+      <x:c r="A111" s="61" t="str"/>
+      <x:c r="B111" s="61" t="str"/>
+      <x:c r="C111" s="61" t="str">
+        <x:v>Operational path</x:v>
+      </x:c>
+      <x:c r="D111" s="65" t="str">
+        <x:v>Supplier/admin can re-run fulfillment as a recovery operation.</x:v>
+      </x:c>
+      <x:c r="E111" s="65" t="str">
+        <x:v>Legacy supplier update ran pending order processing as part of the submit flow.</x:v>
+      </x:c>
+      <x:c r="F111" s="65" t="str">
+        <x:v>Operator can recover if fulfillment needs another pass.</x:v>
+      </x:c>
+      <x:c r="G111" s="65" t="str">
+        <x:v>Partially</x:v>
+      </x:c>
+      <x:c r="H111" s="65" t="str">
+        <x:v>RcvrRequestProcessor.java</x:v>
+      </x:c>
+      <x:c r="I111" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J111" s="65" t="str">
+        <x:v>Destination exposes an explicit fulfillment recovery endpoint and UI button in addition to automatic update-triggered fulfillment.</x:v>
+      </x:c>
+      <x:c r="K111" s="65" t="str">
+        <x:v>SupplierInventoryController.cs; inventory.component.ts</x:v>
+      </x:c>
+      <x:c r="L111" s="65" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M111" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="N111" s="65" t="str">
+        <x:v>specs/013-supplier-role-access/spec.md DP-002, DP-004; specs/013-supplier-role-access/plan.md DD-004</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
